--- a/output/research/multi_factor/factor_collinearity_report_P10.xlsx
+++ b/output/research/multi_factor/factor_collinearity_report_P10.xlsx
@@ -190,12 +190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$B$2:$B$87</f>
+              <f>'corr_series'!$B$2:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$C$2:$C$87</f>
+              <f>'corr_series'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +254,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$D$2:$D$87</f>
+              <f>'corr_series'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$E$2:$E$87</f>
+              <f>'corr_series'!$E$2:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$F$2:$F$87</f>
+              <f>'corr_series'!$F$2:$F$90</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$G$2:$G$87</f>
+              <f>'corr_series'!$G$2:$G$90</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$H$2:$H$87</f>
+              <f>'corr_series'!$H$2:$H$90</f>
             </numRef>
           </val>
         </ser>
@@ -414,12 +414,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$I$2:$I$87</f>
+              <f>'corr_series'!$I$2:$I$90</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$J$2:$J$87</f>
+              <f>'corr_series'!$J$2:$J$90</f>
             </numRef>
           </val>
         </ser>
@@ -478,12 +478,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$87</f>
+              <f>'corr_series'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$K$2:$K$87</f>
+              <f>'corr_series'!$K$2:$K$90</f>
             </numRef>
           </val>
         </ser>
@@ -520,8 +520,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6974468395508909"/>
-          <min val="-0.4408724383919627"/>
+          <max val="1.026934755453718"/>
+          <min val="-1.06924030081061"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -598,12 +598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$B$2:$B$87</f>
+              <f>'cum_corr'!$B$2:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -630,12 +630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$C$2:$C$87</f>
+              <f>'cum_corr'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$D$2:$D$87</f>
+              <f>'cum_corr'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$E$2:$E$87</f>
+              <f>'cum_corr'!$E$2:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$F$2:$F$87</f>
+              <f>'cum_corr'!$F$2:$F$90</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$G$2:$G$87</f>
+              <f>'cum_corr'!$G$2:$G$90</f>
             </numRef>
           </val>
         </ser>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$H$2:$H$87</f>
+              <f>'cum_corr'!$H$2:$H$90</f>
             </numRef>
           </val>
         </ser>
@@ -822,12 +822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$I$2:$I$87</f>
+              <f>'cum_corr'!$I$2:$I$90</f>
             </numRef>
           </val>
         </ser>
@@ -854,12 +854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$J$2:$J$87</f>
+              <f>'cum_corr'!$J$2:$J$90</f>
             </numRef>
           </val>
         </ser>
@@ -886,12 +886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$87</f>
+              <f>'cum_corr'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$K$2:$K$87</f>
+              <f>'cum_corr'!$K$2:$K$90</f>
             </numRef>
           </val>
         </ser>
@@ -928,8 +928,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="21.58825486589501"/>
-          <min val="-9.307767398828307"/>
+          <max val="48.05256614467365"/>
+          <min val="-44.57196283600674"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1321,135 +1321,135 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha084</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>alpha099</t>
+          <t>alpha101</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>alpha027</t>
+          <t>alpha035</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alpha019</t>
+          <t>alpha001</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>alpha046</t>
+          <t>alpha042</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha084</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.027201</v>
+        <v>0.09175999999999999</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.074313</v>
+        <v>0.382563</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.32193</v>
+        <v>0.379008</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.06378300000000001</v>
+        <v>-0.412551</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>alpha099</t>
+          <t>alpha101</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.027201</v>
+        <v>0.09175999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.219104</v>
+        <v>0.09279800000000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.259285</v>
+        <v>-0.074671</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.084407</v>
+        <v>-0.421191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>alpha027</t>
+          <t>alpha035</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.074313</v>
+        <v>0.382563</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.219104</v>
+        <v>0.09279800000000001</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.225824</v>
+        <v>0.413868</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.250983</v>
+        <v>-0.172182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>alpha019</t>
+          <t>alpha001</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.32193</v>
+        <v>0.379008</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.259285</v>
+        <v>-0.074671</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.225824</v>
+        <v>0.413868</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.519846</v>
+        <v>-0.009637</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>alpha046</t>
+          <t>alpha042</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.06378300000000001</v>
+        <v>-0.412551</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.084407</v>
+        <v>-0.421191</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.250983</v>
+        <v>-0.172182</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.519846</v>
+        <v>-0.009637</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -1465,135 +1465,135 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha084</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>alpha099</t>
+          <t>alpha101</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>alpha027</t>
+          <t>alpha035</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>alpha019</t>
+          <t>alpha001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>alpha046</t>
+          <t>alpha042</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha084</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.033106</v>
+        <v>0.118284</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.001046</v>
+        <v>0.490173</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.077624</v>
+        <v>0.41789</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.084207</v>
+        <v>-0.217173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>alpha099</t>
+          <t>alpha101</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.033106</v>
+        <v>0.118284</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.170488</v>
+        <v>0.215844</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.135554</v>
+        <v>0.115253</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.107025</v>
+        <v>-0.411074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>alpha027</t>
+          <t>alpha035</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>-0.001046</v>
+        <v>0.490173</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.170488</v>
+        <v>0.215844</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.121511</v>
+        <v>0.439792</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.100899</v>
+        <v>-0.10508</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>alpha019</t>
+          <t>alpha001</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.077624</v>
+        <v>0.41789</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.135554</v>
+        <v>0.115253</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.121511</v>
+        <v>0.439792</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.318975</v>
+        <v>-0.072071</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>alpha046</t>
+          <t>alpha042</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.084207</v>
+        <v>-0.217173</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.107025</v>
+        <v>-0.411074</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.100899</v>
+        <v>-0.10508</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.318975</v>
+        <v>-0.072071</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1739,52 +1739,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha099</t>
+          <t>alpha084 vs alpha101</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha027</t>
+          <t>alpha084 vs alpha035</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha019</t>
+          <t>alpha084 vs alpha001</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha046</t>
+          <t>alpha084 vs alpha042</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha027</t>
+          <t>alpha101 vs alpha035</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha019</t>
+          <t>alpha101 vs alpha001</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha046</t>
+          <t>alpha101 vs alpha042</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha019</t>
+          <t>alpha035 vs alpha001</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha046</t>
+          <t>alpha035 vs alpha042</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha019 vs alpha046</t>
+          <t>alpha001 vs alpha042</t>
         </is>
       </c>
     </row>
@@ -1795,6 +1795,9 @@
           <t>2023-01-03</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>-0.4113798405233891</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1802,14 +1805,14 @@
           <t>2023-01-18</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0.2937262937810178</v>
+      <c r="G4" t="n">
+        <v>0.8823709584699715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1731034871724744</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.1949635802860465</v>
+        <v>-0.5114850003476515</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.9246765038268633</v>
       </c>
     </row>
     <row r="5">
@@ -1818,20 +1821,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>-0.2078156585338879</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.1581962983817549</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.2378855548858317</v>
+      <c r="G5" t="n">
+        <v>0.5316612216789619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1259215122397431</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.1046460975503042</v>
+        <v>-0.261889151185422</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.696225941145286</v>
       </c>
     </row>
     <row r="6">
@@ -1840,20 +1837,14 @@
           <t>2023-02-15</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.2107426396399989</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.1418105562875054</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.140268293000487</v>
+      <c r="G6" t="n">
+        <v>0.382375401028806</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.07056438657268567</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.02528396423464643</v>
+        <v>-0.2806709307241951</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.03694712147849506</v>
       </c>
     </row>
     <row r="7">
@@ -1863,19 +1854,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2107426396399989</v>
+        <v>0.2563409399447957</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1464295251628442</v>
+        <v>0.571709609247253</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4030387736505973</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2397071474487968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1984325587557795</v>
+        <v>0.1840692127833785</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1269540307058488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1316073060210679</v>
+        <v>-0.3430192137534755</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4022476588223356</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.08039014574357503</v>
+        <v>-0.1823247680925661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1461409394322046</v>
       </c>
     </row>
     <row r="8">
@@ -1885,19 +1891,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.210742639639999</v>
+        <v>-0.08725709478179323</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1630111150704537</v>
+        <v>0.6574215903962731</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4571863805963094</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.3167530613743326</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3227993688095452</v>
+        <v>0.1873707387156186</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1901808954801489</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1852954597362166</v>
+        <v>-0.3302367137534936</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5202651588018754</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3127134592008569</v>
+        <v>-0.2679011917734089</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.1269906396718124</v>
       </c>
     </row>
     <row r="9">
@@ -1907,19 +1928,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2107426396399989</v>
+        <v>-0.2117277241211143</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1510947779720529</v>
+        <v>0.2183612186957637</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2319621515151213</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.3544619590152828</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07872378625742851</v>
+        <v>0.1870600576679952</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.006546669234201055</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1618089191353548</v>
+        <v>-0.324419059793971</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3264613979898532</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04779752153487333</v>
+        <v>-0.1058138810912682</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.0813867056088267</v>
       </c>
     </row>
     <row r="10">
@@ -1929,22 +1965,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2284634020970602</v>
+        <v>0.06408311132770865</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1537350115670228</v>
+        <v>0.4480729128250387</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6198688961317007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1195877886540234</v>
+        <v>-0.3568653659425433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2005036260307262</v>
+        <v>0.08815848047268286</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0985552591731484</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1254846630026997</v>
+        <v>-0.3258760041102026</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4549825404861556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1338530762801135</v>
+        <v>-0.05012433700836223</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.2997635636464382</v>
       </c>
     </row>
     <row r="11">
@@ -1954,19 +2002,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.210742639639999</v>
+        <v>0.06300908336280943</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1441147359394835</v>
+        <v>0.561942538906723</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3820103826786847</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.1299392133106173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2144073904653614</v>
+        <v>0.09208844340315503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2211284845326441</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02776629605525673</v>
+        <v>-0.2799439786018222</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3788208817346164</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04620474043716406</v>
+        <v>-0.07014746566956997</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0743474965925752</v>
       </c>
     </row>
     <row r="12">
@@ -1976,19 +2039,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2167238245368195</v>
+        <v>0.2724046137926688</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1349519921383911</v>
+        <v>0.548012304332983</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4169413900267435</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3076240445749005</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1454664804899016</v>
+        <v>0.1349699457815503</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04886286611639456</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1224721381740421</v>
+        <v>-0.3403315118256853</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4647205147350973</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1227509826453901</v>
+        <v>-0.1220830709023751</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.13234319603225</v>
       </c>
     </row>
     <row r="13">
@@ -1998,19 +2076,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.19649248577246</v>
+        <v>0.4289980999315958</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1581962983817549</v>
+        <v>0.7734753413270792</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3767868494800897</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2428471245862473</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3098579537797803</v>
+        <v>0.5077449579534953</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.169012691362828</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09128617122325783</v>
+        <v>-0.4048771290436315</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4336910365058915</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03031951107655864</v>
+        <v>-0.2925329622197168</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.1655909020866748</v>
       </c>
     </row>
     <row r="14">
@@ -2020,19 +2113,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1857122804094832</v>
+        <v>0.1325608484678933</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.151094777972053</v>
+        <v>0.4368907100865874</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4709026839101682</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.288936886239192</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2251917641290269</v>
+        <v>0.3176344036921074</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2069027712521748</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2139106050506605</v>
+        <v>-0.3462077995934218</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.474432884810209</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0006883477514705834</v>
+        <v>-0.2327987505614899</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.2808660924731122</v>
       </c>
     </row>
     <row r="15">
@@ -2042,19 +2150,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2107426396399989</v>
+        <v>0.09589914504887588</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1395160212830312</v>
+        <v>0.5542344451969363</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4588090708901974</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.1271719462206391</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1864847462881532</v>
+        <v>0.2406740224892108</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2561373564293477</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02190460209431877</v>
+        <v>-0.3402987389689639</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4643162619857625</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.02991153387924824</v>
+        <v>-0.1195774955317959</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.1199598417024529</v>
       </c>
     </row>
     <row r="16">
@@ -2064,19 +2187,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1992687361255656</v>
+        <v>0.1767118955232629</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1372301599078029</v>
+        <v>0.4379222455389029</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4304165595334875</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2603077314928787</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1695513244383158</v>
+        <v>0.1488098142703677</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1310142456754733</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04929170145878805</v>
+        <v>-0.4109053580190923</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5160306860233643</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.735092192893122e-05</v>
+        <v>-0.0637433220344691</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.1003704697589367</v>
       </c>
     </row>
     <row r="17">
@@ -2086,19 +2224,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2167238245368195</v>
+        <v>-0.2305781580574184</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1630111150704537</v>
+        <v>0.4708373076027101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3259233659785804</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1258298245425867</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2581893094760165</v>
+        <v>0.04352559534009069</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2028450655918263</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.03097886708669686</v>
+        <v>-0.3864465390203501</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4085426178367297</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2638059943275927</v>
+        <v>-0.05109487559282785</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.2324148050934032</v>
       </c>
     </row>
     <row r="18">
@@ -2108,19 +2261,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2020803228789259</v>
+        <v>0.1695499282865571</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1654456490020896</v>
+        <v>0.4569598150793399</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2872487264031954</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.130482778691707</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0730202875725629</v>
+        <v>-0.0303012646141269</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.07205186312369555</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05586090325223656</v>
+        <v>-0.4503265500204678</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3730532805247633</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03391653373716233</v>
+        <v>-0.01762020535044231</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01158705484415614</v>
       </c>
     </row>
     <row r="19">
@@ -2130,19 +2298,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2137114306713209</v>
+        <v>0.3161215580741409</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1630111150704537</v>
+        <v>0.5983012192853813</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5206165169165307</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.3858090582228094</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1029124323174433</v>
+        <v>0.3611286940563426</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.26134374588001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.182093944421843</v>
+        <v>-0.3780314257695808</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4313463153172777</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1197576563649298</v>
+        <v>-0.2012860102113606</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.3009566019977475</v>
       </c>
     </row>
     <row r="20">
@@ -2152,22 +2335,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1450290087029011</v>
+        <v>0.3087497486469284</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1637999176320621</v>
+        <v>0.5818911141264926</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2595781140813955</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09050208066706765</v>
+        <v>-0.0764532296128628</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2250860514065848</v>
+        <v>0.1970749577104405</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.01939811490668853</v>
       </c>
       <c r="H20" t="n">
-        <v>0.120604769062001</v>
+        <v>-0.4685836857865315</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4384319950052988</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2384850606863086</v>
+        <v>-0.239819167484234</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.1248979638965962</v>
       </c>
     </row>
     <row r="21">
@@ -2177,22 +2372,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1511265162864019</v>
+        <v>0.09181265767488023</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.09263101300455008</v>
+        <v>0.2470055457578221</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1980837699699961</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.03664473481279144</v>
+        <v>0.02913306809783833</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0941430671725924</v>
+        <v>0.04019612389167378</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.03468205474808978</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03009846159882604</v>
+        <v>-0.5412747588747384</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.198011857344041</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0269942805233844</v>
+        <v>0.09082377832433856</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.02783704653650488</v>
       </c>
     </row>
     <row r="22">
@@ -2202,22 +2409,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1964924857724598</v>
+        <v>0.2204181445556499</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.06944659376793955</v>
+        <v>0.3804073124229633</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.259362749803779</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.09475438866595681</v>
+        <v>-0.1529378610677366</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1365752512400552</v>
+        <v>0.1669012327483268</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.06318721418079253</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.05048103535460044</v>
+        <v>-0.3988027054570328</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4555667803655056</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07473720645555917</v>
+        <v>-0.1614409664913113</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1255887121484579</v>
       </c>
     </row>
     <row r="23">
@@ -2227,19 +2446,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1737620117142288</v>
+        <v>-0.2236071507342174</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1374293752410856</v>
+        <v>0.5344986827624352</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5097257903132838</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2007258363254434</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2152124506156314</v>
+        <v>-0.01423435622057747</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.04701789956992976</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1985488707437744</v>
+        <v>-0.5411369451873212</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2225301228000025</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1039321879095463</v>
+        <v>0.04141901708043965</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.02113570475950333</v>
       </c>
     </row>
     <row r="24">
@@ -2249,19 +2483,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1737620117142288</v>
+        <v>0.1998553193271092</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1482679679745704</v>
+        <v>0.3323899608872271</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2940523658539588</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.4405867092512333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2765265201649867</v>
+        <v>0.1228640125318222</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.0117264402324406</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1451421664027106</v>
+        <v>-0.3439656634111225</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4701148602329101</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1429373690168408</v>
+        <v>0.1191497406332285</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.09510598658744354</v>
       </c>
     </row>
     <row r="25">
@@ -2271,19 +2520,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1916825299398449</v>
+        <v>0.1456177099351424</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1527143493489882</v>
+        <v>0.3338581924335302</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.336503781817051</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.5331374440990166</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1090058579139103</v>
+        <v>-0.01693651234508786</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.07510473245465535</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1285327019389728</v>
+        <v>-0.4034984346673682</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5015055946920743</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1301357207183662</v>
+        <v>-0.09513050436370347</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.02728151965674394</v>
       </c>
     </row>
     <row r="26">
@@ -2293,22 +2557,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1351554025021828</v>
+        <v>-0.09271065787189535</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1395160212830312</v>
+        <v>0.4345993886505555</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4939206234161533</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05612990822204503</v>
+        <v>-0.1214156700868818</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0769400101789733</v>
+        <v>0.1941485300619545</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.004072861859692516</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1502433428387764</v>
+        <v>-0.3239429224477823</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5001144386561032</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2954965200266721</v>
+        <v>-0.02179213600601935</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.02193156426938923</v>
       </c>
     </row>
     <row r="27">
@@ -2318,22 +2594,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1209921139843045</v>
+        <v>0.2153267904181038</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1558140140741855</v>
+        <v>0.4522093816543788</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4821208113184325</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1094079436833159</v>
+        <v>-0.432990390607252</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1705848056019203</v>
+        <v>0.35065075280183</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.183767743262366</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2981871689040564</v>
+        <v>-0.4874039283538817</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6707295756034322</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1635445959722873</v>
+        <v>-0.3122745424190738</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.08261042003881304</v>
       </c>
     </row>
     <row r="28">
@@ -2343,28 +2631,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1890202725795695</v>
+        <v>-0.1132284638763437</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1104090874835196</v>
+        <v>0.8057256963417569</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7603886003142369</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1215912719719917</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1248450141543724</v>
+        <v>-0.1338034444944066</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3258084920561323</v>
+        <v>-0.05275755853608356</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3349249368774587</v>
+        <v>-0.3922412579637693</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006962507023841867</v>
+        <v>0.7207549066742545</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.11798352144227</v>
+        <v>0.2259643641241852</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2722091879272622</v>
+        <v>0.09817242379113326</v>
       </c>
     </row>
     <row r="29">
@@ -2374,34 +2668,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1380559421715735</v>
+        <v>0.1109814454625752</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1418105562875053</v>
+        <v>0.4571926269550615</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08900190308630285</v>
+        <v>0.4365710401983981</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1169721227584247</v>
+        <v>-0.2691714323989687</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1910260386658285</v>
+        <v>0.07841545909790786</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2219526027575535</v>
+        <v>0.01176578954793584</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1765443495494788</v>
+        <v>-0.3627282542480034</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1684484031574332</v>
+        <v>0.4215427054512513</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1014680107301383</v>
+        <v>-0.1404122457037636</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5894926384792001</v>
+        <v>-0.1530623412480151</v>
       </c>
     </row>
     <row r="30">
@@ -2411,28 +2705,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1890202725795695</v>
+        <v>-0.2566871639891243</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1353020182983475</v>
+        <v>0.5797877219198698</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.607256314112144</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1323987592299966</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2319744633842508</v>
+        <v>-0.1367478190196736</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1661654223669532</v>
+        <v>-0.08552728199803313</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1411374527199935</v>
+        <v>-0.4792726869900697</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1164968406703322</v>
+        <v>0.2820832781806339</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2939896137731896</v>
+        <v>0.07225665086452886</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1929404085918137</v>
+        <v>-0.03825568527812174</v>
       </c>
     </row>
     <row r="31">
@@ -2442,28 +2742,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1787211968653991</v>
+        <v>0.298592410255775</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1460703732631967</v>
+        <v>0.5204416112346838</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3180570971128192</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2939091974431081</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02414590982460445</v>
+        <v>0.3863194397035145</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04592206421940961</v>
+        <v>0.05608270068489633</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02575967387231781</v>
+        <v>-0.4220644761815322</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1232446830476908</v>
+        <v>0.3512974467629479</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08106564026053921</v>
+        <v>-0.2335700261234664</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4487464073376456</v>
+        <v>0.09678721720596802</v>
       </c>
     </row>
     <row r="32">
@@ -2473,28 +2779,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1838036555234517</v>
+        <v>0.2970079830738592</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1227465847333876</v>
+        <v>0.5834904516220467</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5316435947748401</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.4158851101406159</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2539754504269776</v>
+        <v>0.1190547176286295</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1667283013474746</v>
+        <v>0.2102430375534383</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3245881274838883</v>
+        <v>-0.4442177963424788</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0753257869605387</v>
+        <v>0.4571003035796339</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2481275749176493</v>
+        <v>-0.1825363457245918</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06797236042686931</v>
+        <v>-0.1534797574614759</v>
       </c>
     </row>
     <row r="33">
@@ -2504,28 +2816,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1812463559520403</v>
+        <v>-0.1364673665493865</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1438886157672385</v>
+        <v>0.6503683491754393</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4681080370548812</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.03134105826916291</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2249338527106093</v>
+        <v>-0.08610367574029762</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1826134841491253</v>
+        <v>0.03596641497583764</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1413720549194712</v>
+        <v>-0.4760955991650037</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02367748268420092</v>
+        <v>0.5075364613375914</v>
       </c>
       <c r="J33" t="n">
-        <v>0.006017132120234045</v>
+        <v>-0.06819419408635259</v>
       </c>
       <c r="K33" t="n">
-        <v>0.379874665707963</v>
+        <v>-0.2381389041791908</v>
       </c>
     </row>
     <row r="34">
@@ -2535,31 +2853,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1812463559520403</v>
+        <v>-0.08085428921078781</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1838036555234518</v>
+        <v>0.4499586189650838</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.5216010145093348</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01663010893723959</v>
+        <v>-0.09969958048933562</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08935921591221258</v>
+        <v>-0.2219872300692298</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.01188816754191113</v>
+        <v>-0.2126461529890546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1572159566444654</v>
+        <v>-0.4444613659176626</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1582125933229769</v>
+        <v>0.577674550615644</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04428219136726426</v>
+        <v>0.1888581960733861</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3009267802610376</v>
+        <v>0.1693381193621973</v>
       </c>
     </row>
     <row r="35">
@@ -2569,34 +2890,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1661155106119585</v>
+        <v>0.04215802475702087</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1093922496904076</v>
+        <v>0.3216385984137303</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1703088600627004</v>
+        <v>0.3245350323178187</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1511254460903626</v>
+        <v>-0.03790994081109422</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1400399069660162</v>
+        <v>0.1510547091514118</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02750445636984244</v>
+        <v>0.1231932545297485</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0174252667367248</v>
+        <v>-0.5241160622895066</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1083322485058775</v>
+        <v>0.1861316914565466</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1487499835412608</v>
+        <v>-0.08707827508313624</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2979888349659866</v>
+        <v>-0.05498293081991264</v>
       </c>
     </row>
     <row r="36">
@@ -2606,28 +2927,34 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1374444522110988</v>
+        <v>0.2332663306446808</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.112334534400814</v>
+        <v>0.5672197995681347</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6831258192989662</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.4962747236749053</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1111929292763296</v>
+        <v>0.306254076471593</v>
       </c>
       <c r="G36" t="n">
-        <v>0.09184536734866695</v>
+        <v>0.1878842650202225</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07046136335673142</v>
+        <v>-0.460195729507167</v>
       </c>
       <c r="I36" t="n">
-        <v>0.188732271265144</v>
+        <v>0.5101472760601098</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04785143138247926</v>
+        <v>-0.1896311251751874</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2872314931323956</v>
+        <v>-0.1301588270378272</v>
       </c>
     </row>
     <row r="37">
@@ -2637,34 +2964,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0883971824327921</v>
+        <v>-0.2108477561541041</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.04007316022734381</v>
+        <v>0.3184571656159833</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06048684647232055</v>
+        <v>0.4119846888338113</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0836293623180384</v>
+        <v>-0.2485845360766206</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07402332101976047</v>
+        <v>0.05086432344822113</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0421621574115565</v>
+        <v>-0.2717008381942679</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.005122012349535885</v>
+        <v>-0.4704598782497346</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.05283676870897929</v>
+        <v>0.3897069885294512</v>
       </c>
       <c r="J37" t="n">
-        <v>0.08683487977854927</v>
+        <v>-0.1280033044868752</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1262894492116175</v>
+        <v>0.01207062859769359</v>
       </c>
     </row>
     <row r="38">
@@ -2674,28 +3001,34 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.133630620956212</v>
+        <v>0.2054806640803817</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1089902839136482</v>
+        <v>0.6037781161754334</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.4850262004758723</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.1694555081206986</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2878618594532406</v>
+        <v>0.406846577513062</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2932104815960771</v>
+        <v>0.08212859184976093</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2070020688189842</v>
+        <v>-0.4144391595183803</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1869026314447499</v>
+        <v>0.2954454894232637</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2449006078941345</v>
+        <v>-0.2045930573802266</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5431399566748595</v>
+        <v>-0.05549684119480966</v>
       </c>
     </row>
     <row r="39">
@@ -2705,28 +3038,34 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.1413530862085967</v>
+        <v>0.2553929420168944</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1174440439029409</v>
+        <v>0.5580404483399423</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5123960804007331</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.4845780068683473</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2574370076358481</v>
+        <v>0.3079207769979608</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1215130586467258</v>
+        <v>0.2535081965098693</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09247550139297137</v>
+        <v>-0.3945141914294286</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0419383183615468</v>
+        <v>0.5543683491707408</v>
       </c>
       <c r="J39" t="n">
-        <v>0.001122131234389503</v>
+        <v>-0.2352266448234113</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3147481895461406</v>
+        <v>-0.2471000408925382</v>
       </c>
     </row>
     <row r="40">
@@ -2736,28 +3075,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.1393864104874338</v>
+        <v>-0.07300703036226386</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.107334697685273</v>
+        <v>0.4830162283934716</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.52642949704661</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.005768005232606628</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2708527385642827</v>
+        <v>0.3261989948675805</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0988245533432161</v>
+        <v>-0.0008820478578149293</v>
       </c>
       <c r="H40" t="n">
-        <v>0.175055328861821</v>
+        <v>-0.4406119263981503</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1158560439950347</v>
+        <v>0.4352671000786015</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1502881580043014</v>
+        <v>-0.2228848955757627</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1943482767892135</v>
+        <v>0.06059515439928885</v>
       </c>
     </row>
     <row r="41">
@@ -2767,28 +3112,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1393864104874338</v>
+        <v>0.3904967590791572</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1089902839136482</v>
+        <v>0.5370792903813126</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4977177738067548</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.3411786079415349</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1827567511441421</v>
+        <v>0.276911140366685</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2912531926230223</v>
+        <v>0.1528864400867176</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0730843442745691</v>
+        <v>-0.4514061665542544</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1049047569737832</v>
+        <v>0.4246458183018006</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1151594820385767</v>
+        <v>-0.02006111749555773</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2520417052352348</v>
+        <v>0.01190573902228917</v>
       </c>
     </row>
     <row r="42">
@@ -2798,28 +3149,34 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.133630620956212</v>
+        <v>0.08936023902046927</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1174440439029408</v>
+        <v>0.3749313197881407</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3993101821461461</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.07444995861148698</v>
       </c>
       <c r="F42" t="n">
-        <v>0.102011783343331</v>
+        <v>-0.2306714393626512</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1935229335810308</v>
+        <v>0.008594714308492337</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08611425053369995</v>
+        <v>-0.5178714105775228</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1463083671172514</v>
+        <v>0.1666589266949144</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1933243562533818</v>
+        <v>0.06776476582133124</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3031039553739369</v>
+        <v>0.06486560521576695</v>
       </c>
     </row>
     <row r="43">
@@ -2829,28 +3186,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1413530862085966</v>
+        <v>-0.1963124865338499</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.128070747644091</v>
+        <v>0.3599613929062686</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.2730063321853934</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1011189609103945</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1388278396813196</v>
+        <v>-0.1512544645047025</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0003713086380707083</v>
+        <v>0.3379148148428832</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.03827279466522374</v>
+        <v>-0.5333625370373712</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1406073950803977</v>
+        <v>-0.02852584552485676</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1996144933152365</v>
+        <v>-0.04496875593416856</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.006478471556029931</v>
+        <v>-0.1372440016086703</v>
       </c>
     </row>
     <row r="44">
@@ -2860,28 +3223,34 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1413530862085966</v>
+        <v>0.3632308359111989</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1174440439029408</v>
+        <v>0.3524782003140726</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.07591297508306941</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.5283865136892297</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0006014883355978183</v>
+        <v>0.300440156611727</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006913929951764728</v>
+        <v>0.03507558306732625</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03688868874122982</v>
+        <v>-0.4102470774017498</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1371563179016386</v>
+        <v>0.3659156568280952</v>
       </c>
       <c r="J44" t="n">
-        <v>0.05706666359265976</v>
+        <v>-0.05057404477629488</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3437139053387884</v>
+        <v>0.09245099709036715</v>
       </c>
     </row>
     <row r="45">
@@ -2891,34 +3260,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.07428966838182745</v>
+        <v>-0.3271571882477848</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.05602474698879131</v>
+        <v>0.6573135754323072</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1199229069488544</v>
+        <v>0.6058291920234982</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.006345057167069333</v>
+        <v>0.06538862485887814</v>
       </c>
       <c r="F45" t="n">
-        <v>0.09555015392970502</v>
+        <v>-0.1465688591929455</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1866585351862864</v>
+        <v>-0.299641149607676</v>
       </c>
       <c r="H45" t="n">
-        <v>0.03518462912360597</v>
+        <v>-0.4601291357253741</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.02684357173721798</v>
+        <v>0.3612779052669289</v>
       </c>
       <c r="J45" t="n">
-        <v>0.06243871848271047</v>
+        <v>0.06792984272767001</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1038113172052173</v>
+        <v>0.1348806979413693</v>
       </c>
     </row>
     <row r="46">
@@ -2928,28 +3297,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1393864104874338</v>
+        <v>0.2584860858414237</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1123345344008139</v>
+        <v>0.5648702591641424</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5899591200058034</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.3508205370980599</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3420352015349858</v>
+        <v>0.4362987819183528</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2606976572232882</v>
+        <v>0.3543501332561741</v>
       </c>
       <c r="H46" t="n">
-        <v>0.296938172139224</v>
+        <v>-0.4487443481477421</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1266605256593488</v>
+        <v>0.5694700395255421</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1453487520533628</v>
+        <v>-0.2682707014319794</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6150017704160229</v>
+        <v>-0.2558856903191686</v>
       </c>
     </row>
     <row r="47">
@@ -2959,28 +3334,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1393864104874338</v>
+        <v>-0.07938981995446398</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1056892272937854</v>
+        <v>0.4760193320994076</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4283415923200937</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.0631810001456525</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1386507484204357</v>
+        <v>0.2233869688301325</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.05238484015392209</v>
+        <v>0.1629792418777158</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.06140526946431695</v>
+        <v>-0.4534736920672113</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3263985566284278</v>
+        <v>0.4282423868951357</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1786871823806016</v>
+        <v>-0.1664718483353979</v>
       </c>
       <c r="K47" t="n">
-        <v>0.226172065240938</v>
+        <v>-0.1565381235635868</v>
       </c>
     </row>
     <row r="48">
@@ -2990,28 +3371,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1433455447702488</v>
+        <v>-0.1277608452231352</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1157275124715691</v>
+        <v>0.5501626701382486</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.525428339915913</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.2476276346186477</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4335264760997324</v>
+        <v>0.05725061019789104</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2528926675632092</v>
+        <v>-0.03861462172859072</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2580117543478356</v>
+        <v>-0.4456783244827207</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1546489146699552</v>
+        <v>0.5255284973536375</v>
       </c>
       <c r="J48" t="n">
-        <v>0.109333098636687</v>
+        <v>-0.06926507830900694</v>
       </c>
       <c r="K48" t="n">
-        <v>0.278919556367212</v>
+        <v>-0.003523324314021553</v>
       </c>
     </row>
     <row r="49">
@@ -3021,31 +3408,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1515960634700893</v>
+        <v>0.2320199976215355</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.02154336745161308</v>
+        <v>0.3635242950064836</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.4011141656516933</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.001528583428479364</v>
+        <v>0.1211329089425425</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3424201353691254</v>
+        <v>0.06086978933995429</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3386695638070376</v>
+        <v>0.1002430442911491</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1254813588937444</v>
+        <v>-0.4526547375738938</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2179283007083183</v>
+        <v>0.2455849643997018</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06911965685560539</v>
+        <v>0.05272740899841734</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3099644194271624</v>
+        <v>0.05580473110573182</v>
       </c>
     </row>
     <row r="50">
@@ -3055,28 +3445,34 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1323210687994431</v>
+        <v>-0.01171674105214787</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1012609553666858</v>
+        <v>0.5307910263791445</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.453888285896085</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.07431547746616614</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3176655454398467</v>
+        <v>0.1611985211441286</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2951856396038918</v>
+        <v>0.1088959813478119</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1439520535608699</v>
+        <v>-0.4985771590748855</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1800078158383991</v>
+        <v>0.3567290269445063</v>
       </c>
       <c r="J50" t="n">
-        <v>0.123830617902694</v>
+        <v>-0.06869135577444901</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4298623823469335</v>
+        <v>-0.02749714896993109</v>
       </c>
     </row>
     <row r="51">
@@ -3086,28 +3482,34 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1233379585935061</v>
+        <v>-0.07629184372684869</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.09838071519901918</v>
+        <v>0.16541362782696</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01996558034972159</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.2168214227352927</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.02810316594123786</v>
+        <v>0.1502647098462037</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3282412338910234</v>
+        <v>-0.04198243253337856</v>
       </c>
       <c r="H51" t="n">
-        <v>0.04148659311480942</v>
+        <v>-0.4437393163657229</v>
       </c>
       <c r="I51" t="n">
-        <v>0.06527982857321273</v>
+        <v>0.2230598521975617</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2187057346515923</v>
+        <v>-0.05703640787627754</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2307389671948316</v>
+        <v>0.144858019745395</v>
       </c>
     </row>
     <row r="52">
@@ -3117,34 +3519,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.03764616262105232</v>
+        <v>0.1909462198821725</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.02154336745161314</v>
+        <v>0.4678922100047864</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1266061158603292</v>
+        <v>0.2972750293140241</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1176466043327404</v>
+        <v>-0.01865583434412891</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1076832055237</v>
+        <v>0.386089244434726</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1378921435969462</v>
+        <v>0.2194453109839701</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1048534047249751</v>
+        <v>-0.4828788532210561</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1371335740967083</v>
+        <v>0.2596049491781481</v>
       </c>
       <c r="J52" t="n">
-        <v>0.107422949517113</v>
+        <v>-0.239861570446607</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4367054913513121</v>
+        <v>-0.08504253220193841</v>
       </c>
     </row>
     <row r="53">
@@ -3154,28 +3556,34 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1102635692839942</v>
+        <v>0.03362304400067942</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.08070466898086182</v>
+        <v>0.5303052784099489</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.1279692767041261</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1376221183472928</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.006970714806775202</v>
+        <v>0.1058318399747624</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.3623676606028003</v>
+        <v>-0.005574754941048821</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.02109390160183735</v>
+        <v>-0.4441241057845816</v>
       </c>
       <c r="I53" t="n">
-        <v>0.04589690507021008</v>
+        <v>0.2572215244414953</v>
       </c>
       <c r="J53" t="n">
-        <v>0.008018798815541963</v>
+        <v>0.04917444947663092</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08087536298740094</v>
+        <v>0.1355997735783757</v>
       </c>
     </row>
     <row r="54">
@@ -3185,34 +3593,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.139386410487434</v>
+        <v>0.07361672913287926</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1174440439029408</v>
+        <v>0.6618756209133778</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1117570378429426</v>
+        <v>0.4426537920233379</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01524202163769468</v>
+        <v>-0.268977411291082</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1041186743495366</v>
+        <v>0.1459187271004043</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3097539770062859</v>
+        <v>0.2158126892737544</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1841090672118887</v>
+        <v>-0.5258208463011924</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2311980656945798</v>
+        <v>0.4395098523513944</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.02398431776034317</v>
+        <v>-0.182171918797879</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3479984463218053</v>
+        <v>-0.04041187998085208</v>
       </c>
     </row>
     <row r="55">
@@ -3222,28 +3630,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1268454332888114</v>
+        <v>-0.08137157228168643</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1071968152299286</v>
+        <v>0.274297641311234</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2442499983646518</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.148611714693323</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1694925919367845</v>
+        <v>0.2085207945978667</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2507759872010954</v>
+        <v>0.2828483566251142</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2565320588440302</v>
+        <v>-0.4897157464594805</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2001065524683977</v>
+        <v>0.4906426228165822</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2644514045245692</v>
+        <v>-0.09719656742774919</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5527051710230581</v>
+        <v>-0.2539234595208525</v>
       </c>
     </row>
     <row r="56">
@@ -3253,28 +3667,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1233379585935061</v>
+        <v>0.04102744959092519</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.09981407910902304</v>
+        <v>0.5509551083324791</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5317709119296707</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.1889487662478215</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1856696087039262</v>
+        <v>0.2340099481636196</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0371704922828467</v>
+        <v>0.01458887966237961</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1106827271181461</v>
+        <v>-0.4478087547428615</v>
       </c>
       <c r="I56" t="n">
-        <v>0.04675788927281604</v>
+        <v>0.5181079684096017</v>
       </c>
       <c r="J56" t="n">
-        <v>0.06510701893758362</v>
+        <v>0.03304494052439125</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2757243954241755</v>
+        <v>0.02592610144285526</v>
       </c>
     </row>
     <row r="57">
@@ -3284,31 +3704,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1134042331421657</v>
+        <v>-0.2899112168776772</v>
       </c>
       <c r="C57" t="n">
-        <v>0.01425965765074889</v>
+        <v>0.7633492895729298</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3512695646987922</v>
       </c>
       <c r="E57" t="n">
-        <v>0.09839004128625031</v>
+        <v>-0.03602389065564097</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1962559012456229</v>
+        <v>-0.2992124364976976</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06781595105649316</v>
+        <v>0.04347877033270652</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1063130110074461</v>
+        <v>-0.3554419388122448</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1623937727680042</v>
+        <v>0.315727382331158</v>
       </c>
       <c r="J57" t="n">
-        <v>0.01562704367831863</v>
+        <v>0.05163622268830778</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4001310789852119</v>
+        <v>-0.04596738196942347</v>
       </c>
     </row>
     <row r="58">
@@ -3318,28 +3741,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.09323508829909925</v>
+        <v>0.04801100811965332</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.07237920675576852</v>
+        <v>0.5508584038310952</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.052035300373355</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.04653632559857297</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1222924763921006</v>
+        <v>0.1936517643037971</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.02050648155456842</v>
+        <v>0.2416341918725112</v>
       </c>
       <c r="H58" t="n">
-        <v>0.005529479433426313</v>
+        <v>-0.3837712274593727</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1667667807449416</v>
+        <v>0.3155926481113156</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.03311319390528697</v>
+        <v>-0.01088219825503765</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.02274697097271773</v>
+        <v>-0.0617206056979952</v>
       </c>
     </row>
     <row r="59">
@@ -3349,28 +3778,34 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.08333333333333326</v>
+        <v>-0.4304579555982818</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.07033025476334581</v>
+        <v>0.6469823524868273</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.7143897202382111</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1524660690467187</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06516475582592497</v>
+        <v>-0.06080533092216776</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.206084593262753</v>
+        <v>-0.4323619170736641</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1021576252241473</v>
+        <v>-0.4566026166111423</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.06320984501571503</v>
+        <v>0.4296046934667692</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.03474289224398705</v>
+        <v>0.04880523761261724</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2063142061193872</v>
+        <v>0.2186027120643539</v>
       </c>
     </row>
     <row r="60">
@@ -3380,28 +3815,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.08333333333333323</v>
+        <v>0.405541020184275</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.07341911803280055</v>
+        <v>0.3820360124718749</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.01136398920321502</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.518034018623852</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.09078708143840929</v>
+        <v>0.1593715874607842</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.1386722827267753</v>
+        <v>-0.1928346038336045</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1680335477231499</v>
+        <v>-0.4459616351101909</v>
       </c>
       <c r="I60" t="n">
-        <v>0.12706172625978</v>
+        <v>0.5778254514141976</v>
       </c>
       <c r="J60" t="n">
-        <v>0.09340889405386352</v>
+        <v>-0.140327213311211</v>
       </c>
       <c r="K60" t="n">
-        <v>0.371964955200368</v>
+        <v>0.05591489386600606</v>
       </c>
     </row>
     <row r="61">
@@ -3411,28 +3852,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.08569751680368515</v>
+        <v>0.3061599500327953</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.06932028853554488</v>
+        <v>0.2531775044622432</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3954832963492007</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.6769515529845123</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1536103463398144</v>
+        <v>0.3099928776840649</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1099616682522262</v>
+        <v>0.392354351038234</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2775860066619318</v>
+        <v>-0.3790878787432603</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0397620121145748</v>
+        <v>0.3864058608935058</v>
       </c>
       <c r="J61" t="n">
-        <v>0.06930540812945413</v>
+        <v>-0.05490173035540902</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3961591334625823</v>
+        <v>-0.1821718032530256</v>
       </c>
     </row>
     <row r="62">
@@ -3442,28 +3889,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.07990604811790904</v>
+        <v>0.1316593840444233</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.06536687218393283</v>
+        <v>0.6455018546479266</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.5655845526501491</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.336813207701277</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1062450665456986</v>
+        <v>0.3499275121570288</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3307156750672212</v>
+        <v>0.3066805229709979</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2425730647689651</v>
+        <v>-0.4406437527352527</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.02446257121299245</v>
+        <v>0.7239999501033928</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.02208847083319406</v>
+        <v>-0.1651182520364438</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4741149183037095</v>
+        <v>-0.2072907818142827</v>
       </c>
     </row>
     <row r="63">
@@ -3473,34 +3926,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.0008328753777787151</v>
+        <v>0.2607728523619751</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03564349655273723</v>
+        <v>0.529099422625005</v>
       </c>
       <c r="D63" t="n">
-        <v>0.09403533674948802</v>
+        <v>0.1817409092218542</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1247299999621694</v>
+        <v>-0.1031910082916697</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2137825521404359</v>
+        <v>0.3393455283288641</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3717978019044921</v>
+        <v>0.1505297640527478</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1293093261471341</v>
+        <v>-0.4577365915325719</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1571007485499741</v>
+        <v>0.2848349056382139</v>
       </c>
       <c r="J63" t="n">
-        <v>0.04686853443206698</v>
+        <v>-0.1281130620659408</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4268889354167084</v>
+        <v>-0.2078694325755401</v>
       </c>
     </row>
     <row r="64">
@@ -3510,34 +3963,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.009188630773666261</v>
+        <v>0.3766251640320567</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.102721992025739</v>
+        <v>0.5331423915790524</v>
       </c>
       <c r="D64" t="n">
-        <v>0.07256183588607053</v>
+        <v>0.4624488339867477</v>
       </c>
       <c r="E64" t="n">
-        <v>0.08351882502290309</v>
+        <v>-0.2522834040278175</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0807244761062626</v>
+        <v>0.3446469888878935</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1794068048883942</v>
+        <v>0.1471819946789916</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1101371900723753</v>
+        <v>-0.4108365513402557</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.006119955913069565</v>
+        <v>0.5926943611300345</v>
       </c>
       <c r="J64" t="n">
-        <v>0.08997982481188815</v>
+        <v>0.02459105293868242</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1892665227265365</v>
+        <v>0.06997448451560287</v>
       </c>
     </row>
     <row r="65">
@@ -3547,28 +4000,34 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.07990604811790904</v>
+        <v>0.2286022111224769</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0703302547633458</v>
+        <v>0.5059851508481977</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.4729213983147949</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.3475291659922845</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1153658463916655</v>
+        <v>0.3883893939604425</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1668815229498266</v>
+        <v>0.3408646000289828</v>
       </c>
       <c r="H65" t="n">
-        <v>0.04529171192930493</v>
+        <v>-0.5487998387051102</v>
       </c>
       <c r="I65" t="n">
-        <v>0.125985759259241</v>
+        <v>0.5900822340747165</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1891081331758061</v>
+        <v>-0.3315741541459891</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4733946218806517</v>
+        <v>-0.2429073077143089</v>
       </c>
     </row>
     <row r="66">
@@ -3578,34 +4037,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.1216235992670947</v>
+        <v>0.299759584394501</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.09276994905294821</v>
+        <v>0.4226207561976753</v>
       </c>
       <c r="D66" t="n">
-        <v>0.07299948450098818</v>
+        <v>0.4579510188259557</v>
       </c>
       <c r="E66" t="n">
-        <v>0.07691773599694453</v>
+        <v>-0.3209096089048665</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1894799489138807</v>
+        <v>0.3513063231422698</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2784558741902757</v>
+        <v>0.2477058676498022</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1966723288596479</v>
+        <v>-0.3522540790684821</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09676668758444903</v>
+        <v>0.4476064325170945</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2253763998239282</v>
+        <v>-0.0690724161643726</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3229990261424724</v>
+        <v>0.1011651717126382</v>
       </c>
     </row>
     <row r="67">
@@ -3615,28 +4074,34 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.08450704225352119</v>
+        <v>-0.02743108939904519</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.07134974196115187</v>
+        <v>0.4808464369257257</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.478679268472846</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.3389728185398775</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2893628423980049</v>
+        <v>0.2063473940137644</v>
       </c>
       <c r="G67" t="n">
-        <v>0.218765527127072</v>
+        <v>0.1857596233326266</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1178788366105071</v>
+        <v>-0.5290328144398374</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2409177370652101</v>
+        <v>0.5511475373668788</v>
       </c>
       <c r="J67" t="n">
-        <v>0.1134396933741719</v>
+        <v>-0.1009647946311659</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4426811700435153</v>
+        <v>-0.1731237023275935</v>
       </c>
     </row>
     <row r="68">
@@ -3646,28 +4111,34 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.08217570104462958</v>
+        <v>0.1808961657175066</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0683193978637673</v>
+        <v>0.4982102484605226</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.5594552414239961</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.3017063525074395</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2257778535676575</v>
+        <v>0.3231227749648538</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.000540194044900528</v>
+        <v>0.06898860524400945</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.01540091995384686</v>
+        <v>-0.4891968083085824</v>
       </c>
       <c r="I68" t="n">
-        <v>0.05558020223569553</v>
+        <v>0.4745001125287157</v>
       </c>
       <c r="J68" t="n">
-        <v>0.1285174563292619</v>
+        <v>-0.1995353814359659</v>
       </c>
       <c r="K68" t="n">
-        <v>0.3723138228271484</v>
+        <v>-0.0438018511356178</v>
       </c>
     </row>
     <row r="69">
@@ -3677,34 +4148,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.0008328753777789333</v>
+        <v>-0.2115077423218242</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01940834977861456</v>
+        <v>0.340450556721492</v>
       </c>
       <c r="D69" t="n">
-        <v>0.07544214663174817</v>
+        <v>0.557289355840218</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1204332296586801</v>
+        <v>-0.05999069778515471</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2207878126242311</v>
+        <v>0.1433345901777259</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3068798410215121</v>
+        <v>-0.2265024377559518</v>
       </c>
       <c r="H69" t="n">
-        <v>0.316672958537415</v>
+        <v>-0.4199476974776437</v>
       </c>
       <c r="I69" t="n">
-        <v>0.09670991903407797</v>
+        <v>0.365020181420815</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2482595170414376</v>
+        <v>0.03294109486327086</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4887764512373916</v>
+        <v>0.003945269161292096</v>
       </c>
     </row>
     <row r="70">
@@ -3713,23 +4184,35 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>0.1744444984163009</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.5117789741274781</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.3157805381338914</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.2211878178468051</v>
+      </c>
       <c r="F70" t="n">
-        <v>0.1212252834461369</v>
+        <v>0.4528792506648661</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2363159703465706</v>
+        <v>0.2461889948247926</v>
       </c>
       <c r="H70" t="n">
-        <v>0.07194177972824081</v>
+        <v>-0.4310714843939781</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3358006555396553</v>
+        <v>0.3967663487535314</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1621651357110876</v>
+        <v>-0.1548674229270822</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2932344217686482</v>
+        <v>-0.08232882382753504</v>
       </c>
     </row>
     <row r="71">
@@ -3739,34 +4222,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.08690547593388663</v>
+        <v>0.3948568010570847</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.07033025476334583</v>
+        <v>0.4738573510585866</v>
       </c>
       <c r="D71" t="n">
-        <v>0.05492502569403366</v>
+        <v>0.5015803508174737</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08074466302656906</v>
+        <v>-0.2480814742156246</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2140965402292599</v>
+        <v>0.4943250286477948</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3556969897488861</v>
+        <v>0.2982036139549534</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1385932432017759</v>
+        <v>-0.4377490416252023</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1475685384802354</v>
+        <v>0.4652861399183098</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1418372518464815</v>
+        <v>-0.2345200464374447</v>
       </c>
       <c r="K71" t="n">
-        <v>0.215691213189858</v>
+        <v>-0.2133600127434444</v>
       </c>
     </row>
     <row r="72">
@@ -3775,23 +4258,35 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="B72" t="n">
+        <v>0.2112962009478955</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.373934502157004</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.3821489284525468</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.1885484391744659</v>
+      </c>
       <c r="F72" t="n">
-        <v>0.3365044648890025</v>
+        <v>0.396949510571462</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1470872534254294</v>
+        <v>0.3380436298547487</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1046629389021915</v>
+        <v>-0.4685736353252729</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1871611599472587</v>
+        <v>0.3851594054692153</v>
       </c>
       <c r="J72" t="n">
-        <v>0.02135980500485557</v>
+        <v>-0.04627264628073456</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2183830982644354</v>
+        <v>-0.06659517797791362</v>
       </c>
     </row>
     <row r="73">
@@ -3800,23 +4295,35 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>0.09188082783845371</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.3815759799234191</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.5717019090784875</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.3778270962937267</v>
+      </c>
       <c r="F73" t="n">
-        <v>0.1297852263285619</v>
+        <v>-0.05269283262462363</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1101570643737091</v>
+        <v>-0.06189012447471275</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2650542511840038</v>
+        <v>-0.4820022774203954</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1472667117132984</v>
+        <v>0.5000687387255389</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1067069835831813</v>
+        <v>-0.01100098217951567</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3037053122128642</v>
+        <v>0.006126764809728677</v>
       </c>
     </row>
     <row r="74">
@@ -3825,23 +4332,35 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>0.2204190669929014</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.560244237405641</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.4112834053439018</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.2660891502570135</v>
+      </c>
       <c r="F74" t="n">
-        <v>0.2282858928472341</v>
+        <v>0.4678369126687099</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2739854410538231</v>
+        <v>0.293724086453702</v>
       </c>
       <c r="H74" t="n">
-        <v>0.142335137005355</v>
+        <v>-0.4562333502593207</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2834686638316494</v>
+        <v>0.5040179237122578</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0596184233719016</v>
+        <v>-0.2250498573308798</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3637709442751319</v>
+        <v>-0.1123991369925833</v>
       </c>
     </row>
     <row r="75">
@@ -3850,23 +4369,35 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>-0.008429064790111317</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.5239876141936606</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.4518143619208299</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.1406687981850155</v>
+      </c>
       <c r="F75" t="n">
-        <v>0.08906615753530248</v>
+        <v>0.08080767878863331</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2401530985838918</v>
+        <v>-0.3138642699144203</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1579856538270904</v>
+        <v>-0.4735605473629652</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0872187601794483</v>
+        <v>0.3629668015559717</v>
       </c>
       <c r="J75" t="n">
-        <v>0.092537516829448</v>
+        <v>-0.1640283835792344</v>
       </c>
       <c r="K75" t="n">
-        <v>0.4756599613542613</v>
+        <v>0.1709232840072788</v>
       </c>
     </row>
     <row r="76">
@@ -3876,34 +4407,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.08450704225352115</v>
+        <v>0.5392055187749699</v>
       </c>
       <c r="C76" t="n">
-        <v>0.09591852517188471</v>
+        <v>0.3049249455792186</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08662083924813026</v>
+        <v>0.2280711911565493</v>
       </c>
       <c r="E76" t="n">
-        <v>0.07074938739647887</v>
+        <v>-0.5889524789982503</v>
       </c>
       <c r="F76" t="n">
-        <v>0.03434120037018097</v>
+        <v>0.4349578036016481</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.02504279767913357</v>
+        <v>0.319325184801772</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1056382681941687</v>
+        <v>-0.4573258013501525</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1858432503538201</v>
+        <v>0.5587994271768535</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03187290702114389</v>
+        <v>-0.1446010013883625</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3165217818417362</v>
+        <v>-0.03028415913678015</v>
       </c>
     </row>
     <row r="77">
@@ -3912,23 +4443,35 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>0.1433874591695743</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.5838445996563004</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.5444619651869659</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.1695292896622836</v>
+      </c>
       <c r="F77" t="n">
-        <v>0.2130780139055367</v>
+        <v>0.3285880289654001</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2420588641857857</v>
+        <v>0.1947195740613896</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1615958939976293</v>
+        <v>-0.5608846753961443</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.05773316969938153</v>
+        <v>0.5942816337549288</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0005281833038213149</v>
+        <v>-0.2087943722626152</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3508907398529556</v>
+        <v>-0.1374398361933907</v>
       </c>
     </row>
     <row r="78">
@@ -3937,23 +4480,35 @@
           <t>2025-12-30</t>
         </is>
       </c>
+      <c r="B78" t="n">
+        <v>-0.001909092627633642</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.548211359502741</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4547553870778816</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.1003590083223625</v>
+      </c>
       <c r="F78" t="n">
-        <v>0.06778969179620321</v>
+        <v>0.1330293746878858</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1147444762442587</v>
+        <v>0.04494701720031826</v>
       </c>
       <c r="H78" t="n">
-        <v>0.01993397439085313</v>
+        <v>-0.5401713524103974</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1133708307620115</v>
+        <v>0.4499292355879584</v>
       </c>
       <c r="J78" t="n">
-        <v>0.06914404921670302</v>
+        <v>0.0728856006347951</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2217070060762792</v>
+        <v>0.04196662730460847</v>
       </c>
     </row>
     <row r="79">
@@ -3962,23 +4517,35 @@
           <t>2026-01-14</t>
         </is>
       </c>
+      <c r="B79" t="n">
+        <v>0.182762296058331</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.5256889347058102</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.6119539615512958</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.2635204352227433</v>
+      </c>
       <c r="F79" t="n">
-        <v>0.2335754309273655</v>
+        <v>0.4258419649471532</v>
       </c>
       <c r="G79" t="n">
-        <v>0.252332529996434</v>
+        <v>0.2690255742999184</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2214877614049178</v>
+        <v>-0.3560191663083844</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2274607975205767</v>
+        <v>0.6075878236961453</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1251240177323836</v>
+        <v>0.05731167931327427</v>
       </c>
       <c r="K79" t="n">
-        <v>0.4130085890063737</v>
+        <v>-0.05489283517401092</v>
       </c>
     </row>
     <row r="80">
@@ -3987,23 +4554,35 @@
           <t>2026-01-29</t>
         </is>
       </c>
+      <c r="B80" t="n">
+        <v>0.08013391210290684</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.6522096770290766</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.5184663795486338</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.2311466800111236</v>
+      </c>
       <c r="F80" t="n">
-        <v>0.2516297091929393</v>
+        <v>0.3798522533676802</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3208343950052109</v>
+        <v>0.2708851554331841</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1190458442489613</v>
+        <v>-0.4119717180008278</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2111235625440701</v>
+        <v>0.6504897401140912</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1490264267277116</v>
+        <v>-0.1599390052846301</v>
       </c>
       <c r="K80" t="n">
-        <v>0.6189420617617286</v>
+        <v>-0.08974819389593298</v>
       </c>
     </row>
     <row r="81">
@@ -4013,34 +4592,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.07990604811790908</v>
+        <v>0.3811764611428273</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.07769309688655061</v>
+        <v>0.5553714307478919</v>
       </c>
       <c r="D81" t="n">
-        <v>0.09795621206216784</v>
+        <v>0.6718588838040952</v>
       </c>
       <c r="E81" t="n">
-        <v>0.08173817613677326</v>
+        <v>-0.390966019912576</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2355140195572866</v>
+        <v>0.613166234205394</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.07342368740673366</v>
+        <v>0.144988134955756</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00228650777129814</v>
+        <v>-0.5564868708463667</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1679484893896905</v>
+        <v>0.4286938033088585</v>
       </c>
       <c r="J81" t="n">
-        <v>0.1664062726908892</v>
+        <v>-0.2864089151064199</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4180390942058005</v>
+        <v>-0.07572874715484416</v>
       </c>
     </row>
     <row r="82">
@@ -4049,23 +4628,35 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="B82" t="n">
+        <v>0.04562378446965877</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.4979604429199297</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.4285751825687306</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.05459074704352281</v>
+      </c>
       <c r="F82" t="n">
-        <v>0.1559026728581495</v>
+        <v>0.3902886365366289</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1652634092168399</v>
+        <v>0.2005553965187575</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1690260062390218</v>
+        <v>-0.47640136544412</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2122779830770629</v>
+        <v>0.5074656119471407</v>
       </c>
       <c r="J82" t="n">
-        <v>0.06082255920116105</v>
+        <v>-0.1824953936939929</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1199421258337414</v>
+        <v>-0.08795114194524793</v>
       </c>
     </row>
     <row r="83">
@@ -4074,23 +4665,35 @@
           <t>2026-03-13</t>
         </is>
       </c>
+      <c r="B83" t="n">
+        <v>0.08203857351078486</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.4185475183246748</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.3658532466807634</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-0.2047445856290348</v>
+      </c>
       <c r="F83" t="n">
-        <v>0.1595006864608777</v>
+        <v>0.3313732158908709</v>
       </c>
       <c r="G83" t="n">
-        <v>0.01838575761681319</v>
+        <v>0.1924659937873852</v>
       </c>
       <c r="H83" t="n">
-        <v>0.06571705144052313</v>
+        <v>-0.5653775747974696</v>
       </c>
       <c r="I83" t="n">
-        <v>0.179399551585347</v>
+        <v>0.4205342761888721</v>
       </c>
       <c r="J83" t="n">
-        <v>0.2103773999378265</v>
+        <v>-0.07426572785299142</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4202240346346371</v>
+        <v>-0.05584717549646618</v>
       </c>
     </row>
     <row r="84">
@@ -4099,23 +4702,35 @@
           <t>2026-03-27</t>
         </is>
       </c>
+      <c r="B84" t="n">
+        <v>0.3156823738968523</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.574441293167026</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.5150609108847131</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-0.2835632297092761</v>
+      </c>
       <c r="F84" t="n">
-        <v>-0.01788533204874322</v>
+        <v>0.3340569423027311</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.2106035785629324</v>
+        <v>0.1788674283626611</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.03048452402302099</v>
+        <v>-0.5233120262374054</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1055086949738591</v>
+        <v>0.4691458141188887</v>
       </c>
       <c r="J84" t="n">
-        <v>0.06153683337760462</v>
+        <v>-0.1458635741261819</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1811826203625848</v>
+        <v>-0.009749090954852288</v>
       </c>
     </row>
     <row r="85">
@@ -4124,23 +4739,35 @@
           <t>2026-04-13</t>
         </is>
       </c>
+      <c r="B85" t="n">
+        <v>0.374108299462087</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.3087367966606611</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.5006962706293212</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-0.5566283823814967</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.2298642499074587</v>
+        <v>0.5345976576676605</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3450078241199694</v>
+        <v>0.3570197931780889</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2383098069891619</v>
+        <v>-0.3333551657061136</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1914110209096992</v>
+        <v>0.248729726894576</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1494497387756616</v>
+        <v>-0.2790659528896009</v>
       </c>
       <c r="K85" t="n">
-        <v>0.3548311290280645</v>
+        <v>-0.1369402886272866</v>
       </c>
     </row>
     <row r="86">
@@ -4149,23 +4776,35 @@
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="B86" t="n">
+        <v>-0.03858449206065485</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.3848139838476838</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.3948659624837877</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-0.2126201227211346</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3593681567984275</v>
+        <v>0.4967230051014194</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3054651696543556</v>
+        <v>0.04971132731516575</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07906700578074256</v>
+        <v>-0.4235383656769574</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1107417531936869</v>
+        <v>0.2090636941934128</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0712329393455719</v>
+        <v>-0.2904393448218309</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1438855454832004</v>
+        <v>-0.0980350781172967</v>
       </c>
     </row>
     <row r="87">
@@ -4174,23 +4813,35 @@
           <t>2026-05-11</t>
         </is>
       </c>
+      <c r="B87" t="n">
+        <v>0.5488249677079621</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.6813339784685731</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.4315058565492598</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.4723511070181822</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.1877950571919586</v>
+        <v>0.7498302760121314</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3326884286982736</v>
+        <v>0.3675490667982667</v>
       </c>
       <c r="H87" t="n">
-        <v>0.06415094699695939</v>
+        <v>-0.5008154316130876</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0717362958662717</v>
+        <v>0.4590464313736375</v>
       </c>
       <c r="J87" t="n">
-        <v>0.08549395362627456</v>
+        <v>-0.4191545101756469</v>
       </c>
       <c r="K87" t="n">
-        <v>0.3092830825930277</v>
+        <v>-0.1601364730695623</v>
       </c>
     </row>
     <row r="88">
@@ -4199,23 +4850,146 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="B88" t="n">
+        <v>0.2032244158119253</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.4869933132780864</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.519268841286207</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.4535264659846197</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.1108486128284266</v>
+        <v>0.5828555158953196</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1755142731084054</v>
+        <v>0.4615655237003652</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.01820070543379673</v>
+        <v>-0.3091632403896927</v>
       </c>
       <c r="I88" t="n">
-        <v>0.08041120451552063</v>
+        <v>0.6510528691258102</v>
       </c>
       <c r="J88" t="n">
-        <v>0.04633638961121415</v>
+        <v>-0.2363881256473492</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3795649878389025</v>
+        <v>-0.2076656258220012</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.520395422753358</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.6857245599187668</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.5143670078531415</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-0.1664371421757219</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.5596833385669021</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.5290782732680818</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.309661607858491</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.498019543657973</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-0.2504088638517004</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.0005762982996083482</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.3513898062116069</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.4398884807039731</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.4305353941380911</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-0.2956718131220507</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.5456063716092643</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.450102364038199</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.3185952571598379</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.5216476926400796</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-0.1932560521890778</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.1783282563697154</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.3073407132669174</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.2903501217297924</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.3476280684368148</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-0.2080205719895494</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.415976290026332</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.105206831316675</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.2558763147293633</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.2921385636838628</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-0.2177772517987392</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-0.1344707679031493</v>
       </c>
     </row>
   </sheetData>
@@ -4230,7 +5004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4239,52 +5013,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha099</t>
+          <t>alpha084 vs alpha101</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha027</t>
+          <t>alpha084 vs alpha035</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha019</t>
+          <t>alpha084 vs alpha001</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha046</t>
+          <t>alpha084 vs alpha042</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha027</t>
+          <t>alpha101 vs alpha035</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha019</t>
+          <t>alpha101 vs alpha001</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha046</t>
+          <t>alpha101 vs alpha042</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha019</t>
+          <t>alpha035 vs alpha001</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha046</t>
+          <t>alpha035 vs alpha042</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha019 vs alpha046</t>
+          <t>alpha001 vs alpha042</t>
         </is>
       </c>
     </row>
@@ -4295,6 +5069,9 @@
           <t>2023-01-03</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>-0.4113798405233891</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4302,14 +5079,14 @@
           <t>2023-01-18</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0.2937262937810178</v>
+      <c r="G4" t="n">
+        <v>0.8823709584699715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1731034871724744</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.1949635802860465</v>
+        <v>-0.9228648408710406</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.9246765038268633</v>
       </c>
     </row>
     <row r="5">
@@ -4318,20 +5095,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>-0.2078156585338879</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.1581962983817549</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5316118486668495</v>
+      <c r="G5" t="n">
+        <v>1.414032180148933</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2990249994122175</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.2996096778363507</v>
+        <v>-1.184753992056462</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.620902444972149</v>
       </c>
     </row>
     <row r="6">
@@ -4340,20 +5111,14 @@
           <t>2023-02-15</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.002926981106110949</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.3000068546692604</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6718801416673365</v>
+      <c r="G6" t="n">
+        <v>1.796407581177739</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2284606128395318</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.2743257136017043</v>
+        <v>-1.465424922780658</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.657849566450645</v>
       </c>
     </row>
     <row r="7">
@@ -4363,19 +5128,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2136696207461098</v>
+        <v>0.2563409399447957</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4464363798321046</v>
+        <v>0.571709609247253</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4030387736505973</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2397071474487968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8703127004231159</v>
+        <v>0.1840692127833785</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.923361611883588</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3600679188605997</v>
+        <v>-1.808444136534133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4022476588223356</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1939355678581292</v>
+        <v>-0.1823247680925661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.803990505882849</v>
       </c>
     </row>
     <row r="8">
@@ -4385,19 +5165,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4244122603861088</v>
+        <v>0.1690838451630025</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6094474949025583</v>
+        <v>1.229131199643526</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8602251542469068</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.5564602088231294</v>
       </c>
       <c r="F8" t="n">
-        <v>1.193112069232661</v>
+        <v>0.3714399514989971</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.113542507363737</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5453633785968164</v>
+        <v>-2.138680850287627</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.922512817624211</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5066490270589861</v>
+        <v>-0.450225959865975</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.930981145554661</v>
       </c>
     </row>
     <row r="9">
@@ -4407,19 +5202,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6351549000261076</v>
+        <v>-0.04264387895811184</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7605422728746113</v>
+        <v>1.44749241833929</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.092187305762028</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.9109221678384123</v>
       </c>
       <c r="F9" t="n">
-        <v>1.27183585549009</v>
+        <v>0.5585000091669923</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.106995838129536</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3835544594614616</v>
+        <v>-2.463099910081598</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.248974215614064</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5544465485938594</v>
+        <v>-0.5560398409572432</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-2.012367851163488</v>
       </c>
     </row>
     <row r="10">
@@ -4429,22 +5239,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8636183021231678</v>
+        <v>0.02143923236959681</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9142772844416341</v>
+        <v>1.895565331164329</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.712056201893729</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1195877886540234</v>
+        <v>-1.267787533780956</v>
       </c>
       <c r="F10" t="n">
-        <v>1.472339481520816</v>
+        <v>0.6466584896396751</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.205551097302684</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5090391224641613</v>
+        <v>-2.7889759141918</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.70395675610022</v>
       </c>
       <c r="J10" t="n">
-        <v>0.688299624873973</v>
+        <v>-0.6061641779656055</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.312131414809927</v>
       </c>
     </row>
     <row r="11">
@@ -4454,19 +5276,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.074360941763167</v>
+        <v>0.08444831573240624</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.058392020381118</v>
+        <v>2.457507870071051</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.094066584572413</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.397726747091573</v>
       </c>
       <c r="F11" t="n">
-        <v>1.686746871986177</v>
+        <v>0.7387469330428301</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.426679581835328</v>
       </c>
       <c r="H11" t="n">
-        <v>0.536805418519418</v>
+        <v>-3.068919892793622</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.082777637834836</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7345043653111371</v>
+        <v>-0.6763116436351755</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-2.237783918217352</v>
       </c>
     </row>
     <row r="12">
@@ -4476,19 +5313,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.291084766299986</v>
+        <v>0.356852929525075</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.193344012519509</v>
+        <v>3.005520174404034</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.511007974599157</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.705350791666474</v>
       </c>
       <c r="F12" t="n">
-        <v>1.832213352476079</v>
+        <v>0.8737168788243804</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.475542447951722</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4143332803453759</v>
+        <v>-3.409251404619308</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.547498152569934</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8572553479565271</v>
+        <v>-0.7983947145375506</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-2.370127114249602</v>
       </c>
     </row>
     <row r="13">
@@ -4498,19 +5350,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.094592280527526</v>
+        <v>0.7858510294566708</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.351540310901264</v>
+        <v>3.778995515731113</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.887794824079247</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.948197916252721</v>
       </c>
       <c r="F13" t="n">
-        <v>2.142071306255859</v>
+        <v>1.381461836777876</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.64455513931455</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5056194515686337</v>
+        <v>-3.814128533662939</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.981189189075825</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8875748590330858</v>
+        <v>-1.090927676757267</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-2.535718016336276</v>
       </c>
     </row>
     <row r="14">
@@ -4520,19 +5387,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.28030456093701</v>
+        <v>0.9184118779245641</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.502635088873316</v>
+        <v>4.215886225817701</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.358697507989415</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.237134802491913</v>
       </c>
       <c r="F14" t="n">
-        <v>2.367263070384886</v>
+        <v>1.699096240469983</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.851457910566725</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7195300566192943</v>
+        <v>-4.16033633325636</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.455622073886034</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8868865112816152</v>
+        <v>-1.323726427318757</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2.816584108809389</v>
       </c>
     </row>
     <row r="15">
@@ -4542,19 +5424,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.491047200577009</v>
+        <v>1.01431102297344</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.642151110156348</v>
+        <v>4.770120671014637</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.817506578879612</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.364306748712552</v>
       </c>
       <c r="F15" t="n">
-        <v>2.553747816673039</v>
+        <v>1.939770262959194</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.107595266996073</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6976254545249755</v>
+        <v>-4.500635072225324</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.919938335871797</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8569749774023669</v>
+        <v>-1.443303922850553</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-2.936543950511842</v>
       </c>
     </row>
     <row r="16">
@@ -4564,19 +5461,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.291778464451443</v>
+        <v>1.191022918496703</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.779381270064151</v>
+        <v>5.20804291655354</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.2479231384131</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.624614480205431</v>
       </c>
       <c r="F16" t="n">
-        <v>2.723299141111355</v>
+        <v>2.088580077229561</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.238609512671546</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7469171559837635</v>
+        <v>-4.911540430244417</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.435969021895161</v>
       </c>
       <c r="J16" t="n">
-        <v>0.856877626480438</v>
+        <v>-1.507047244885022</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-3.036914420270778</v>
       </c>
     </row>
     <row r="17">
@@ -4586,19 +5498,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.508502288988262</v>
+        <v>0.9604447604392845</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.942392385134604</v>
+        <v>5.678880224156249</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.57384650439168</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.750444304748018</v>
       </c>
       <c r="F17" t="n">
-        <v>2.981488450587371</v>
+        <v>2.132105672569652</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.441454578263372</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7159382888970667</v>
+        <v>-5.297986969264767</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.844511639731891</v>
       </c>
       <c r="J17" t="n">
-        <v>1.120683620808031</v>
+        <v>-1.55814212047785</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-3.269329225364181</v>
       </c>
     </row>
     <row r="18">
@@ -4608,19 +5535,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.710582611867188</v>
+        <v>1.129994688725842</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.107838034136694</v>
+        <v>6.135840039235589</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.861095230794875</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.880927083439725</v>
       </c>
       <c r="F18" t="n">
-        <v>3.054508738159934</v>
+        <v>2.101804407955525</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.369402715139676</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6600773856448301</v>
+        <v>-5.748313519285235</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.217564920256654</v>
       </c>
       <c r="J18" t="n">
-        <v>1.154600154545193</v>
+        <v>-1.575762325828292</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3.257742170520025</v>
       </c>
     </row>
     <row r="19">
@@ -4630,19 +5572,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.924294042538509</v>
+        <v>1.446116246799983</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.270849149207148</v>
+        <v>6.73414125852097</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.381711747711406</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.266736141662534</v>
       </c>
       <c r="F19" t="n">
-        <v>3.157421170477377</v>
+        <v>2.462933102011868</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.630746461019686</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8421713300666731</v>
+        <v>-6.126344945054815</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.648911235573932</v>
       </c>
       <c r="J19" t="n">
-        <v>1.034842498180263</v>
+        <v>-1.777048336039653</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-3.558698772517773</v>
       </c>
     </row>
     <row r="20">
@@ -4652,22 +5609,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.06932305124141</v>
+        <v>1.754865995446911</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.43464906683921</v>
+        <v>7.316032372647463</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.641289861792801</v>
       </c>
       <c r="E20" t="n">
-        <v>0.210089869321091</v>
+        <v>-3.343189371275397</v>
       </c>
       <c r="F20" t="n">
-        <v>3.382507221883962</v>
+        <v>2.660008059722308</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.611348346112998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9627760991286741</v>
+        <v>-6.594928630841347</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.087343230579231</v>
       </c>
       <c r="J20" t="n">
-        <v>1.273327558866572</v>
+        <v>-2.016867503523887</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-3.683596736414369</v>
       </c>
     </row>
     <row r="21">
@@ -4677,22 +5646,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.918196534955008</v>
+        <v>1.846678653121791</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.52728007984376</v>
+        <v>7.563037918405285</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.839373631762797</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1734451345082996</v>
+        <v>-3.314056303177559</v>
       </c>
       <c r="F21" t="n">
-        <v>3.476650289056554</v>
+        <v>2.700204183613982</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.576666291364908</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9928745607275001</v>
+        <v>-7.136203389716085</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.285355087923272</v>
       </c>
       <c r="J21" t="n">
-        <v>1.300321839389956</v>
+        <v>-1.926043725199548</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-3.711433782950873</v>
       </c>
     </row>
     <row r="22">
@@ -4702,22 +5683,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.114689020727468</v>
+        <v>2.067096797677441</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.596726673611699</v>
+        <v>7.943445230828248</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.098736381566576</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07869074584234276</v>
+        <v>-3.466994164245295</v>
       </c>
       <c r="F22" t="n">
-        <v>3.61322554029661</v>
+        <v>2.867105416362309</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.513479077184116</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9423935253728997</v>
+        <v>-7.535006095173118</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.740921868288778</v>
       </c>
       <c r="J22" t="n">
-        <v>1.375059045845515</v>
+        <v>-2.08748469169086</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-3.837022495099331</v>
       </c>
     </row>
     <row r="23">
@@ -4727,19 +5720,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.288451032441697</v>
+        <v>1.843489646943223</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.734156048852785</v>
+        <v>8.477943913590682</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.60846217187986</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.266268327919852</v>
       </c>
       <c r="F23" t="n">
-        <v>3.828437990912241</v>
+        <v>2.852871060141731</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.466461177614186</v>
       </c>
       <c r="H23" t="n">
-        <v>1.140942396116674</v>
+        <v>-8.07614304036044</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.96345199108878</v>
       </c>
       <c r="J23" t="n">
-        <v>1.478991233755062</v>
+        <v>-2.04606567461042</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-3.815886790339828</v>
       </c>
     </row>
     <row r="24">
@@ -4749,19 +5757,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.462213044155925</v>
+        <v>2.043344966270332</v>
       </c>
       <c r="C24" t="n">
-        <v>-2.882424016827355</v>
+        <v>8.810333874477909</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.902514537733818</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.706855037171085</v>
       </c>
       <c r="F24" t="n">
-        <v>4.104964511077227</v>
+        <v>2.975735072673553</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.454734737381745</v>
       </c>
       <c r="H24" t="n">
-        <v>1.286084562519385</v>
+        <v>-8.420108703771563</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.43356685132169</v>
       </c>
       <c r="J24" t="n">
-        <v>1.621928602771902</v>
+        <v>-1.926915933977192</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-3.910992776927272</v>
       </c>
     </row>
     <row r="25">
@@ -4771,19 +5794,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.27053051421608</v>
+        <v>2.188962676205475</v>
       </c>
       <c r="C25" t="n">
-        <v>-3.035138366176343</v>
+        <v>9.144192066911438</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.239018319550869</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.239992481270102</v>
       </c>
       <c r="F25" t="n">
-        <v>4.213970368991138</v>
+        <v>2.958798560328465</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.37963000492709</v>
       </c>
       <c r="H25" t="n">
-        <v>1.414617264458357</v>
+        <v>-8.823607138438931</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7.935072446013764</v>
       </c>
       <c r="J25" t="n">
-        <v>1.752064323490269</v>
+        <v>-2.022046438340895</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-3.938274296584015</v>
       </c>
     </row>
     <row r="26">
@@ -4793,22 +5831,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.405685916718263</v>
+        <v>2.096252018333579</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.174654387459375</v>
+        <v>9.578791455561994</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.732938942967023</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02256083762029772</v>
+        <v>-4.361408151356984</v>
       </c>
       <c r="F26" t="n">
-        <v>4.290910379170112</v>
+        <v>3.15294709039042</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.375557143067398</v>
       </c>
       <c r="H26" t="n">
-        <v>1.564860607297134</v>
+        <v>-9.147550060886713</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.435186884669868</v>
       </c>
       <c r="J26" t="n">
-        <v>2.047560843516941</v>
+        <v>-2.043838574346915</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.960205860853405</v>
       </c>
     </row>
     <row r="27">
@@ -4818,22 +5868,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.284693802733959</v>
+        <v>2.311578808751683</v>
       </c>
       <c r="C27" t="n">
-        <v>-3.33046840153356</v>
+        <v>10.03100083721637</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.215059754285456</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1319687813036136</v>
+        <v>-4.794398541964235</v>
       </c>
       <c r="F27" t="n">
-        <v>4.461495184772032</v>
+        <v>3.50359784319225</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.559324886329764</v>
       </c>
       <c r="H27" t="n">
-        <v>1.86304777620119</v>
+        <v>-9.634953989240595</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.105916460273299</v>
       </c>
       <c r="J27" t="n">
-        <v>2.211105439489228</v>
+        <v>-2.356113116765989</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-4.042816280892218</v>
       </c>
     </row>
     <row r="28">
@@ -4843,28 +5905,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.473714075313528</v>
+        <v>2.19835034487534</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.44087748901708</v>
+        <v>10.83672653355813</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8.975448354599692</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-4.672807269992243</v>
       </c>
       <c r="F28" t="n">
-        <v>4.586340198926404</v>
+        <v>3.369794398697843</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3258084920561323</v>
+        <v>3.50656732779368</v>
       </c>
       <c r="H28" t="n">
-        <v>2.197972713078649</v>
+        <v>-10.02719524720436</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006962507023841867</v>
+        <v>9.826671366947554</v>
       </c>
       <c r="J28" t="n">
-        <v>2.093121918046958</v>
+        <v>-2.130148752641803</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2722091879272622</v>
+        <v>-3.944643857101085</v>
       </c>
     </row>
     <row r="29">
@@ -4874,34 +5942,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.611770017485102</v>
+        <v>2.309331790337915</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.582688045304586</v>
+        <v>11.29391916051319</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08900190308630285</v>
+        <v>9.41201939479809</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2489409040620383</v>
+        <v>-4.941978702391213</v>
       </c>
       <c r="F29" t="n">
-        <v>4.777366237592233</v>
+        <v>3.448209857795751</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5477610948136857</v>
+        <v>3.518333117341616</v>
       </c>
       <c r="H29" t="n">
-        <v>2.374517062628128</v>
+        <v>-10.38992350145237</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1754109101812751</v>
+        <v>10.24821407239881</v>
       </c>
       <c r="J29" t="n">
-        <v>2.194589928777096</v>
+        <v>-2.270560998345567</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8617018264064623</v>
+        <v>-4.0977061983491</v>
       </c>
     </row>
     <row r="30">
@@ -4911,28 +5979,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.800790290064671</v>
+        <v>2.052644626348791</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.717990063602933</v>
+        <v>11.87370688243306</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10.01927570891023</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4.809579943161216</v>
       </c>
       <c r="F30" t="n">
-        <v>5.009340700976484</v>
+        <v>3.311462038776078</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7139265171806389</v>
+        <v>3.432805835343582</v>
       </c>
       <c r="H30" t="n">
-        <v>2.515654515348122</v>
+        <v>-10.86919618844244</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2919077508516073</v>
+        <v>10.53029735057944</v>
       </c>
       <c r="J30" t="n">
-        <v>2.488579542550286</v>
+        <v>-2.198304347481038</v>
       </c>
       <c r="K30" t="n">
-        <v>1.054642234998276</v>
+        <v>-4.135961883627222</v>
       </c>
     </row>
     <row r="31">
@@ -4942,28 +6016,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.97951148693007</v>
+        <v>2.351237036604565</v>
       </c>
       <c r="C31" t="n">
-        <v>-3.86406043686613</v>
+        <v>12.39414849366774</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10.33733280602305</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-5.103489140604324</v>
       </c>
       <c r="F31" t="n">
-        <v>5.033486610801089</v>
+        <v>3.697781478479592</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7598485814000485</v>
+        <v>3.488888536028479</v>
       </c>
       <c r="H31" t="n">
-        <v>2.541414189220439</v>
+        <v>-11.29126066462397</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1686630678039164</v>
+        <v>10.88159479734239</v>
       </c>
       <c r="J31" t="n">
-        <v>2.569645182810825</v>
+        <v>-2.431874373604504</v>
       </c>
       <c r="K31" t="n">
-        <v>1.503388642335922</v>
+        <v>-4.039174666421254</v>
       </c>
     </row>
     <row r="32">
@@ -4973,28 +6053,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.163315142453522</v>
+        <v>2.648245019678424</v>
       </c>
       <c r="C32" t="n">
-        <v>-3.986807021599517</v>
+        <v>12.97763894528979</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10.86897640079789</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-5.51937425074494</v>
       </c>
       <c r="F32" t="n">
-        <v>5.287462061228067</v>
+        <v>3.816836196108222</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9265768827475231</v>
+        <v>3.699131573581917</v>
       </c>
       <c r="H32" t="n">
-        <v>2.866002316704328</v>
+        <v>-11.73547846096645</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2439888547644551</v>
+        <v>11.33869510092202</v>
       </c>
       <c r="J32" t="n">
-        <v>2.817772757728474</v>
+        <v>-2.614410719329096</v>
       </c>
       <c r="K32" t="n">
-        <v>1.571361002762791</v>
+        <v>-4.19265442388273</v>
       </c>
     </row>
     <row r="33">
@@ -5004,28 +6090,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.344561498405562</v>
+        <v>2.511777653129038</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.130695637366756</v>
+        <v>13.62800729446523</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11.33708443785277</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-5.550715309014103</v>
       </c>
       <c r="F33" t="n">
-        <v>5.512395913938676</v>
+        <v>3.730732520367924</v>
       </c>
       <c r="G33" t="n">
-        <v>1.109190366896649</v>
+        <v>3.735097988557754</v>
       </c>
       <c r="H33" t="n">
-        <v>3.007374371623799</v>
+        <v>-12.21157406013145</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2676663374486561</v>
+        <v>11.84623156225961</v>
       </c>
       <c r="J33" t="n">
-        <v>2.823789889848709</v>
+        <v>-2.682604913415449</v>
       </c>
       <c r="K33" t="n">
-        <v>1.951235668470754</v>
+        <v>-4.430793328061921</v>
       </c>
     </row>
     <row r="34">
@@ -5035,31 +6127,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.163315142453522</v>
+        <v>2.43092336391825</v>
       </c>
       <c r="C34" t="n">
-        <v>-4.314499292890208</v>
+        <v>14.07796591343031</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11.85868545236211</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2655710129992779</v>
+        <v>-5.650414889503439</v>
       </c>
       <c r="F34" t="n">
-        <v>5.601755129850888</v>
+        <v>3.508745290298694</v>
       </c>
       <c r="G34" t="n">
-        <v>1.097302199354737</v>
+        <v>3.5224518355687</v>
       </c>
       <c r="H34" t="n">
-        <v>3.164590328268264</v>
+        <v>-12.65603542604911</v>
       </c>
       <c r="I34" t="n">
-        <v>0.425878930771633</v>
+        <v>12.42390611287526</v>
       </c>
       <c r="J34" t="n">
-        <v>2.868072081215973</v>
+        <v>-2.493746717342062</v>
       </c>
       <c r="K34" t="n">
-        <v>2.252162448731791</v>
+        <v>-4.261455208699724</v>
       </c>
     </row>
     <row r="35">
@@ -5069,34 +6164,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.32943065306548</v>
+        <v>2.473081388675271</v>
       </c>
       <c r="C35" t="n">
-        <v>-4.423891542580615</v>
+        <v>14.39960451184404</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2593107631490033</v>
+        <v>12.18322048467993</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4166964590896406</v>
+        <v>-5.688324830314533</v>
       </c>
       <c r="F35" t="n">
-        <v>5.741795036816904</v>
+        <v>3.659799999450106</v>
       </c>
       <c r="G35" t="n">
-        <v>1.12480665572458</v>
+        <v>3.645645090098448</v>
       </c>
       <c r="H35" t="n">
-        <v>3.147165061531539</v>
+        <v>-13.18015148833862</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5342111792775104</v>
+        <v>12.6100378043318</v>
       </c>
       <c r="J35" t="n">
-        <v>3.016822064757234</v>
+        <v>-2.580824992425199</v>
       </c>
       <c r="K35" t="n">
-        <v>2.550151283697778</v>
+        <v>-4.316438139519637</v>
       </c>
     </row>
     <row r="36">
@@ -5106,28 +6201,34 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.466875105276579</v>
+        <v>2.706347719319952</v>
       </c>
       <c r="C36" t="n">
-        <v>-4.536226076981429</v>
+        <v>14.96682431141218</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12.86634630397889</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-6.184599553989439</v>
       </c>
       <c r="F36" t="n">
-        <v>5.852987966093234</v>
+        <v>3.966054075921699</v>
       </c>
       <c r="G36" t="n">
-        <v>1.216652023073247</v>
+        <v>3.833529355118671</v>
       </c>
       <c r="H36" t="n">
-        <v>3.21762642488827</v>
+        <v>-13.64034721784579</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7229434505426544</v>
+        <v>13.12018508039191</v>
       </c>
       <c r="J36" t="n">
-        <v>3.064673496139713</v>
+        <v>-2.770456117600386</v>
       </c>
       <c r="K36" t="n">
-        <v>2.837382776830174</v>
+        <v>-4.446596966557464</v>
       </c>
     </row>
     <row r="37">
@@ -5137,34 +6238,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.555272287709371</v>
+        <v>2.495499963165848</v>
       </c>
       <c r="C37" t="n">
-        <v>-4.576299237208773</v>
+        <v>15.28528147702816</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3197976096213238</v>
+        <v>13.27833099281271</v>
       </c>
       <c r="E37" t="n">
-        <v>0.500325821407679</v>
+        <v>-6.433184090066059</v>
       </c>
       <c r="F37" t="n">
-        <v>5.927011287112994</v>
+        <v>4.016918399369921</v>
       </c>
       <c r="G37" t="n">
-        <v>1.17448986566169</v>
+        <v>3.561828516924403</v>
       </c>
       <c r="H37" t="n">
-        <v>3.212504412538735</v>
+        <v>-14.11080709609552</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6701066818336752</v>
+        <v>13.50989206892136</v>
       </c>
       <c r="J37" t="n">
-        <v>3.151508375918262</v>
+        <v>-2.898459422087261</v>
       </c>
       <c r="K37" t="n">
-        <v>2.963672226041791</v>
+        <v>-4.43452633795977</v>
       </c>
     </row>
     <row r="38">
@@ -5174,28 +6275,34 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.421641666753159</v>
+        <v>2.70098062724623</v>
       </c>
       <c r="C38" t="n">
-        <v>-4.685289521122422</v>
+        <v>15.8890595932036</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13.76335719328858</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-6.602639598186758</v>
       </c>
       <c r="F38" t="n">
-        <v>6.214873146566235</v>
+        <v>4.423764976882983</v>
       </c>
       <c r="G38" t="n">
-        <v>1.467700347257767</v>
+        <v>3.643957108774164</v>
       </c>
       <c r="H38" t="n">
-        <v>3.419506481357719</v>
+        <v>-14.5252462556139</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8570093132784251</v>
+        <v>13.80533755834463</v>
       </c>
       <c r="J38" t="n">
-        <v>3.396408983812397</v>
+        <v>-3.103052479467488</v>
       </c>
       <c r="K38" t="n">
-        <v>3.506812182716651</v>
+        <v>-4.49002317915458</v>
       </c>
     </row>
     <row r="39">
@@ -5205,28 +6312,34 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.280288580544562</v>
+        <v>2.956373569263124</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.802733565025362</v>
+        <v>16.44710004154354</v>
+      </c>
+      <c r="D39" t="n">
+        <v>14.27575327368931</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-7.087217605055105</v>
       </c>
       <c r="F39" t="n">
-        <v>6.472310154202082</v>
+        <v>4.731685753880944</v>
       </c>
       <c r="G39" t="n">
-        <v>1.589213405904493</v>
+        <v>3.897465305284033</v>
       </c>
       <c r="H39" t="n">
-        <v>3.51198198275069</v>
+        <v>-14.91976044704333</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8989476316399719</v>
+        <v>14.35970590751537</v>
       </c>
       <c r="J39" t="n">
-        <v>3.397531115046786</v>
+        <v>-3.338279124290899</v>
       </c>
       <c r="K39" t="n">
-        <v>3.821560372262791</v>
+        <v>-4.737123220047118</v>
       </c>
     </row>
     <row r="40">
@@ -5236,28 +6349,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.140902170057128</v>
+        <v>2.88336653890086</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.910068262710635</v>
+        <v>16.93011626993701</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14.80218277073592</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-7.081449599822498</v>
       </c>
       <c r="F40" t="n">
-        <v>6.743162892766365</v>
+        <v>5.057884748748524</v>
       </c>
       <c r="G40" t="n">
-        <v>1.688037959247709</v>
+        <v>3.896583257426218</v>
       </c>
       <c r="H40" t="n">
-        <v>3.687037311612511</v>
+        <v>-15.36037237344148</v>
       </c>
       <c r="I40" t="n">
-        <v>1.014803675635007</v>
+        <v>14.79497300759397</v>
       </c>
       <c r="J40" t="n">
-        <v>3.547819273051088</v>
+        <v>-3.561164019866662</v>
       </c>
       <c r="K40" t="n">
-        <v>4.015908649052005</v>
+        <v>-4.676528065647829</v>
       </c>
     </row>
     <row r="41">
@@ -5267,28 +6386,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.280288580544562</v>
+        <v>3.273863297980018</v>
       </c>
       <c r="C41" t="n">
-        <v>-5.019058546624284</v>
+        <v>17.46719556031832</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15.29990054454268</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.422628207764033</v>
       </c>
       <c r="F41" t="n">
-        <v>6.925919643910507</v>
+        <v>5.334795889115209</v>
       </c>
       <c r="G41" t="n">
-        <v>1.979291151870731</v>
+        <v>4.049469697512936</v>
       </c>
       <c r="H41" t="n">
-        <v>3.76012165588708</v>
+        <v>-15.81177853999573</v>
       </c>
       <c r="I41" t="n">
-        <v>1.11970843260879</v>
+        <v>15.21961882589577</v>
       </c>
       <c r="J41" t="n">
-        <v>3.662978755089664</v>
+        <v>-3.58122513736222</v>
       </c>
       <c r="K41" t="n">
-        <v>4.267950354287239</v>
+        <v>-4.66462232662554</v>
       </c>
     </row>
     <row r="42">
@@ -5298,28 +6423,34 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.14665795958835</v>
+        <v>3.363223537000487</v>
       </c>
       <c r="C42" t="n">
-        <v>-5.136502590527225</v>
+        <v>17.84212688010646</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.69921072668882</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-7.49707816637552</v>
       </c>
       <c r="F42" t="n">
-        <v>7.027931427253837</v>
+        <v>5.104124449752558</v>
       </c>
       <c r="G42" t="n">
-        <v>2.172814085451762</v>
+        <v>4.058064411821428</v>
       </c>
       <c r="H42" t="n">
-        <v>3.84623590642078</v>
+        <v>-16.32964995057326</v>
       </c>
       <c r="I42" t="n">
-        <v>1.266016799726041</v>
+        <v>15.38627775259068</v>
       </c>
       <c r="J42" t="n">
-        <v>3.856303111343046</v>
+        <v>-3.513460371540889</v>
       </c>
       <c r="K42" t="n">
-        <v>4.571054309661176</v>
+        <v>-4.599756721409773</v>
       </c>
     </row>
     <row r="43">
@@ -5329,28 +6460,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.288011045796947</v>
+        <v>3.166911050466637</v>
       </c>
       <c r="C43" t="n">
-        <v>-5.264573338171315</v>
+        <v>18.20208827301273</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.42620439450343</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-7.395959205465125</v>
       </c>
       <c r="F43" t="n">
-        <v>7.166759266935157</v>
+        <v>4.952869985247855</v>
       </c>
       <c r="G43" t="n">
-        <v>2.173185394089833</v>
+        <v>4.395979226664311</v>
       </c>
       <c r="H43" t="n">
-        <v>3.807963111755556</v>
+        <v>-16.86301248761063</v>
       </c>
       <c r="I43" t="n">
-        <v>1.406624194806439</v>
+        <v>15.35775190706583</v>
       </c>
       <c r="J43" t="n">
-        <v>4.055917604658283</v>
+        <v>-3.558429127475057</v>
       </c>
       <c r="K43" t="n">
-        <v>4.564575838105146</v>
+        <v>-4.737000723018443</v>
       </c>
     </row>
     <row r="44">
@@ -5360,28 +6497,34 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.429364132005544</v>
+        <v>3.530141886377836</v>
       </c>
       <c r="C44" t="n">
-        <v>-5.382017382074256</v>
+        <v>18.5545664733268</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.5021173695865</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-7.924345719154355</v>
       </c>
       <c r="F44" t="n">
-        <v>7.167360755270756</v>
+        <v>5.253310141859583</v>
       </c>
       <c r="G44" t="n">
-        <v>2.180099324041598</v>
+        <v>4.431054809731637</v>
       </c>
       <c r="H44" t="n">
-        <v>3.844851800496786</v>
+        <v>-17.27325956501237</v>
       </c>
       <c r="I44" t="n">
-        <v>1.543780512708077</v>
+        <v>15.72366756389392</v>
       </c>
       <c r="J44" t="n">
-        <v>4.112984268250942</v>
+        <v>-3.609003172251352</v>
       </c>
       <c r="K44" t="n">
-        <v>4.908289743443934</v>
+        <v>-4.644549725928076</v>
       </c>
     </row>
     <row r="45">
@@ -5391,34 +6534,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.355074463623716</v>
+        <v>3.202984698130051</v>
       </c>
       <c r="C45" t="n">
-        <v>-5.438042129063048</v>
+        <v>19.21188004875911</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4397205165701782</v>
+        <v>16.10794656161</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4939807642406097</v>
+        <v>-7.858957094295477</v>
       </c>
       <c r="F45" t="n">
-        <v>7.26291090920046</v>
+        <v>5.106741282666637</v>
       </c>
       <c r="G45" t="n">
-        <v>2.366757859227884</v>
+        <v>4.131413660123961</v>
       </c>
       <c r="H45" t="n">
-        <v>3.880036429620391</v>
+        <v>-17.73338870073775</v>
       </c>
       <c r="I45" t="n">
-        <v>1.51693694097086</v>
+        <v>16.08494546916085</v>
       </c>
       <c r="J45" t="n">
-        <v>4.175422986733653</v>
+        <v>-3.541073329523682</v>
       </c>
       <c r="K45" t="n">
-        <v>5.012101060649151</v>
+        <v>-4.509669027986707</v>
       </c>
     </row>
     <row r="46">
@@ -5428,28 +6571,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.215688053136283</v>
+        <v>3.461470783971475</v>
       </c>
       <c r="C46" t="n">
-        <v>-5.550376663463862</v>
+        <v>19.77675030792325</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.6979056816158</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-8.209777631393537</v>
       </c>
       <c r="F46" t="n">
-        <v>7.604946110735447</v>
+        <v>5.54304006458499</v>
       </c>
       <c r="G46" t="n">
-        <v>2.627455516451172</v>
+        <v>4.485763793380135</v>
       </c>
       <c r="H46" t="n">
-        <v>4.176974601759615</v>
+        <v>-18.18213304888549</v>
       </c>
       <c r="I46" t="n">
-        <v>1.643597466630208</v>
+        <v>16.65441550868639</v>
       </c>
       <c r="J46" t="n">
-        <v>4.320771738787016</v>
+        <v>-3.809344030955661</v>
       </c>
       <c r="K46" t="n">
-        <v>5.627102831065174</v>
+        <v>-4.765554718305875</v>
       </c>
     </row>
     <row r="47">
@@ -5459,28 +6608,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.076301642648849</v>
+        <v>3.382080964017011</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.656065890757647</v>
+        <v>20.25276964002266</v>
+      </c>
+      <c r="D47" t="n">
+        <v>17.1262472739359</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-8.27295863153919</v>
       </c>
       <c r="F47" t="n">
-        <v>7.743596859155883</v>
+        <v>5.766427033415122</v>
       </c>
       <c r="G47" t="n">
-        <v>2.57507067629725</v>
+        <v>4.648743035257851</v>
       </c>
       <c r="H47" t="n">
-        <v>4.115569332295298</v>
+        <v>-18.6356067409527</v>
       </c>
       <c r="I47" t="n">
-        <v>1.969996023258636</v>
+        <v>17.08265789558153</v>
       </c>
       <c r="J47" t="n">
-        <v>4.499458921167617</v>
+        <v>-3.975815879291059</v>
       </c>
       <c r="K47" t="n">
-        <v>5.853274896306112</v>
+        <v>-4.922092841869462</v>
       </c>
     </row>
     <row r="48">
@@ -5490,28 +6645,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.9329560978786</v>
+        <v>3.254320118793876</v>
       </c>
       <c r="C48" t="n">
-        <v>-5.771793403229216</v>
+        <v>20.80293231016091</v>
+      </c>
+      <c r="D48" t="n">
+        <v>17.65167561385181</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-8.520586266157837</v>
       </c>
       <c r="F48" t="n">
-        <v>8.177123335255615</v>
+        <v>5.823677643613014</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82796334386046</v>
+        <v>4.610128413529261</v>
       </c>
       <c r="H48" t="n">
-        <v>4.373581086643133</v>
+        <v>-19.08128506543542</v>
       </c>
       <c r="I48" t="n">
-        <v>2.124644937928592</v>
+        <v>17.60818639293516</v>
       </c>
       <c r="J48" t="n">
-        <v>4.608792019804304</v>
+        <v>-4.045080957600065</v>
       </c>
       <c r="K48" t="n">
-        <v>6.132194452673324</v>
+        <v>-4.925616166183484</v>
       </c>
     </row>
     <row r="49">
@@ -5521,31 +6682,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3.084552161348689</v>
+        <v>3.486340116415411</v>
       </c>
       <c r="C49" t="n">
-        <v>-5.793336770680829</v>
+        <v>21.1664566051674</v>
+      </c>
+      <c r="D49" t="n">
+        <v>18.05278977950351</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4924521808121303</v>
+        <v>-8.399453357215295</v>
       </c>
       <c r="F49" t="n">
-        <v>8.51954347062474</v>
+        <v>5.884547432952968</v>
       </c>
       <c r="G49" t="n">
-        <v>3.166632907667497</v>
+        <v>4.71037145782041</v>
       </c>
       <c r="H49" t="n">
-        <v>4.499062445536878</v>
+        <v>-19.53393980300932</v>
       </c>
       <c r="I49" t="n">
-        <v>2.34257323863691</v>
+        <v>17.85377135733486</v>
       </c>
       <c r="J49" t="n">
-        <v>4.677911676659909</v>
+        <v>-3.992353548601648</v>
       </c>
       <c r="K49" t="n">
-        <v>6.442158872100486</v>
+        <v>-4.869811435077752</v>
       </c>
     </row>
     <row r="50">
@@ -5555,28 +6719,34 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.216873230148132</v>
+        <v>3.474623375363263</v>
       </c>
       <c r="C50" t="n">
-        <v>-5.894597726047516</v>
+        <v>21.69724763154654</v>
+      </c>
+      <c r="D50" t="n">
+        <v>18.50667806539959</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-8.473768834681461</v>
       </c>
       <c r="F50" t="n">
-        <v>8.837209016064586</v>
+        <v>6.045745954097097</v>
       </c>
       <c r="G50" t="n">
-        <v>3.461818547271389</v>
+        <v>4.819267439168223</v>
       </c>
       <c r="H50" t="n">
-        <v>4.643014499097748</v>
+        <v>-20.0325169620842</v>
       </c>
       <c r="I50" t="n">
-        <v>2.522581054475309</v>
+        <v>18.21050038427937</v>
       </c>
       <c r="J50" t="n">
-        <v>4.801742294562604</v>
+        <v>-4.061044904376097</v>
       </c>
       <c r="K50" t="n">
-        <v>6.87202125444742</v>
+        <v>-4.897308584047683</v>
       </c>
     </row>
     <row r="51">
@@ -5586,28 +6756,34 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.340211188741638</v>
+        <v>3.398331531636415</v>
       </c>
       <c r="C51" t="n">
-        <v>-5.992978441246534</v>
+        <v>21.8626612593735</v>
+      </c>
+      <c r="D51" t="n">
+        <v>18.52664364574931</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-8.690590257416755</v>
       </c>
       <c r="F51" t="n">
-        <v>8.809105850123348</v>
+        <v>6.196010663943301</v>
       </c>
       <c r="G51" t="n">
-        <v>3.133577313380365</v>
+        <v>4.777285006634844</v>
       </c>
       <c r="H51" t="n">
-        <v>4.684501092212558</v>
+        <v>-20.47625627844992</v>
       </c>
       <c r="I51" t="n">
-        <v>2.587860883048522</v>
+        <v>18.43356023647693</v>
       </c>
       <c r="J51" t="n">
-        <v>5.020448029214196</v>
+        <v>-4.118081312252375</v>
       </c>
       <c r="K51" t="n">
-        <v>7.102760221642251</v>
+        <v>-4.752450564302288</v>
       </c>
     </row>
     <row r="52">
@@ -5617,34 +6793,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.377857351362691</v>
+        <v>3.589277751518587</v>
       </c>
       <c r="C52" t="n">
-        <v>-6.014521808698148</v>
+        <v>22.33055346937829</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5663266324305074</v>
+        <v>18.82391867506334</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6100987851448707</v>
+        <v>-8.709246091760884</v>
       </c>
       <c r="F52" t="n">
-        <v>8.916789055647047</v>
+        <v>6.582099908378026</v>
       </c>
       <c r="G52" t="n">
-        <v>3.271469456977311</v>
+        <v>4.996730317618814</v>
       </c>
       <c r="H52" t="n">
-        <v>4.789354496937532</v>
+        <v>-20.95913513167098</v>
       </c>
       <c r="I52" t="n">
-        <v>2.72499445714523</v>
+        <v>18.69316518565508</v>
       </c>
       <c r="J52" t="n">
-        <v>5.127870978731308</v>
+        <v>-4.357942882698982</v>
       </c>
       <c r="K52" t="n">
-        <v>7.539465712993564</v>
+        <v>-4.837493096504226</v>
       </c>
     </row>
     <row r="53">
@@ -5654,28 +6830,34 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.488120920646685</v>
+        <v>3.622900795519266</v>
       </c>
       <c r="C53" t="n">
-        <v>-6.095226477679009</v>
+        <v>22.86085874778824</v>
+      </c>
+      <c r="D53" t="n">
+        <v>18.95188795176746</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-8.57162397341359</v>
       </c>
       <c r="F53" t="n">
-        <v>8.909818340840273</v>
+        <v>6.687931748352788</v>
       </c>
       <c r="G53" t="n">
-        <v>2.909101796374511</v>
+        <v>4.991155562677766</v>
       </c>
       <c r="H53" t="n">
-        <v>4.768260595335695</v>
+        <v>-21.40325923745556</v>
       </c>
       <c r="I53" t="n">
-        <v>2.770891362215441</v>
+        <v>18.95038671009657</v>
       </c>
       <c r="J53" t="n">
-        <v>5.13588977754685</v>
+        <v>-4.308768433222351</v>
       </c>
       <c r="K53" t="n">
-        <v>7.620341075980964</v>
+        <v>-4.701893322925851</v>
       </c>
     </row>
     <row r="54">
@@ -5685,34 +6867,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.627507331134119</v>
+        <v>3.696517524652146</v>
       </c>
       <c r="C54" t="n">
-        <v>-6.21267052158195</v>
+        <v>23.52273436870162</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4545695945875649</v>
+        <v>19.3945417437908</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6253408067825654</v>
+        <v>-8.840601384704673</v>
       </c>
       <c r="F54" t="n">
-        <v>9.013937015189809</v>
+        <v>6.833850475453192</v>
       </c>
       <c r="G54" t="n">
-        <v>3.218855773380797</v>
+        <v>5.20696825195152</v>
       </c>
       <c r="H54" t="n">
-        <v>4.952369662547584</v>
+        <v>-21.92908008375676</v>
       </c>
       <c r="I54" t="n">
-        <v>3.002089427910021</v>
+        <v>19.38989656244797</v>
       </c>
       <c r="J54" t="n">
-        <v>5.111905459786507</v>
+        <v>-4.49094035202023</v>
       </c>
       <c r="K54" t="n">
-        <v>7.96833952230277</v>
+        <v>-4.742305202906703</v>
       </c>
     </row>
     <row r="55">
@@ -5722,28 +6904,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.75435276442293</v>
+        <v>3.615145952370459</v>
       </c>
       <c r="C55" t="n">
-        <v>-6.319867336811879</v>
+        <v>23.79703201001285</v>
+      </c>
+      <c r="D55" t="n">
+        <v>19.63879174215545</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-8.989213099397995</v>
       </c>
       <c r="F55" t="n">
-        <v>9.183429607126593</v>
+        <v>7.042371270051059</v>
       </c>
       <c r="G55" t="n">
-        <v>3.469631760581892</v>
+        <v>5.489816608576634</v>
       </c>
       <c r="H55" t="n">
-        <v>5.208901721391614</v>
+        <v>-22.41879583021624</v>
       </c>
       <c r="I55" t="n">
-        <v>3.202195980378418</v>
+        <v>19.88053918526455</v>
       </c>
       <c r="J55" t="n">
-        <v>5.376356864311076</v>
+        <v>-4.58813691944798</v>
       </c>
       <c r="K55" t="n">
-        <v>8.521044693325829</v>
+        <v>-4.996228662427556</v>
       </c>
     </row>
     <row r="56">
@@ -5753,28 +6941,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.877690723016436</v>
+        <v>3.656173401961385</v>
       </c>
       <c r="C56" t="n">
-        <v>-6.419681415920902</v>
+        <v>24.34798711834533</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20.17056265408512</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-9.178161865645816</v>
       </c>
       <c r="F56" t="n">
-        <v>9.369099215830518</v>
+        <v>7.276381218214679</v>
       </c>
       <c r="G56" t="n">
-        <v>3.506802252864739</v>
+        <v>5.504405488239013</v>
       </c>
       <c r="H56" t="n">
-        <v>5.31958444850976</v>
+        <v>-22.8666045849591</v>
       </c>
       <c r="I56" t="n">
-        <v>3.248953869651234</v>
+        <v>20.39864715367415</v>
       </c>
       <c r="J56" t="n">
-        <v>5.441463883248659</v>
+        <v>-4.555091978923588</v>
       </c>
       <c r="K56" t="n">
-        <v>8.796769088750004</v>
+        <v>-4.970302560984701</v>
       </c>
     </row>
     <row r="57">
@@ -5784,31 +6978,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.991094956158602</v>
+        <v>3.366262185083707</v>
       </c>
       <c r="C57" t="n">
-        <v>-6.405421758270153</v>
+        <v>25.11133640791826</v>
+      </c>
+      <c r="D57" t="n">
+        <v>20.52183221878392</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7237308480688157</v>
+        <v>-9.214185756301458</v>
       </c>
       <c r="F57" t="n">
-        <v>9.565355117076141</v>
+        <v>6.977168781716982</v>
       </c>
       <c r="G57" t="n">
-        <v>3.574618203921232</v>
+        <v>5.547884258571719</v>
       </c>
       <c r="H57" t="n">
-        <v>5.425897459517206</v>
+        <v>-23.22204652377134</v>
       </c>
       <c r="I57" t="n">
-        <v>3.411347642419238</v>
+        <v>20.71437453600531</v>
       </c>
       <c r="J57" t="n">
-        <v>5.457090926926978</v>
+        <v>-4.50345575623528</v>
       </c>
       <c r="K57" t="n">
-        <v>9.196900167735215</v>
+        <v>-5.016269942954124</v>
       </c>
     </row>
     <row r="58">
@@ -5818,28 +7015,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.897859867859503</v>
+        <v>3.414273193203361</v>
       </c>
       <c r="C58" t="n">
-        <v>-6.477800965025922</v>
+        <v>25.66219481174936</v>
+      </c>
+      <c r="D58" t="n">
+        <v>20.57386751915727</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-9.260722081900031</v>
       </c>
       <c r="F58" t="n">
-        <v>9.687647593468242</v>
+        <v>7.170820546020779</v>
       </c>
       <c r="G58" t="n">
-        <v>3.554111722366664</v>
+        <v>5.789518450444231</v>
       </c>
       <c r="H58" t="n">
-        <v>5.431426938950632</v>
+        <v>-23.60581775123072</v>
       </c>
       <c r="I58" t="n">
-        <v>3.57811442316418</v>
+        <v>21.02996718411663</v>
       </c>
       <c r="J58" t="n">
-        <v>5.423977733021691</v>
+        <v>-4.514337954490318</v>
       </c>
       <c r="K58" t="n">
-        <v>9.174153196762498</v>
+        <v>-5.077990548652119</v>
       </c>
     </row>
     <row r="59">
@@ -5849,28 +7052,34 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.981193201192836</v>
+        <v>2.983815237605079</v>
       </c>
       <c r="C59" t="n">
-        <v>-6.548131219789267</v>
+        <v>26.30917716423618</v>
+      </c>
+      <c r="D59" t="n">
+        <v>21.28825723939548</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-9.108256012853312</v>
       </c>
       <c r="F59" t="n">
-        <v>9.752812349294167</v>
+        <v>7.110015215098611</v>
       </c>
       <c r="G59" t="n">
-        <v>3.348027129103911</v>
+        <v>5.357156533370566</v>
       </c>
       <c r="H59" t="n">
-        <v>5.329269313726485</v>
+        <v>-24.06242036784186</v>
       </c>
       <c r="I59" t="n">
-        <v>3.514904578148465</v>
+        <v>21.4595718775834</v>
       </c>
       <c r="J59" t="n">
-        <v>5.389234840777704</v>
+        <v>-4.465532716877701</v>
       </c>
       <c r="K59" t="n">
-        <v>9.380467402881886</v>
+        <v>-4.859387836587765</v>
       </c>
     </row>
     <row r="60">
@@ -5880,28 +7089,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.064526534526169</v>
+        <v>3.389356257789354</v>
       </c>
       <c r="C60" t="n">
-        <v>-6.621550337822068</v>
+        <v>26.69121317670806</v>
+      </c>
+      <c r="D60" t="n">
+        <v>21.27689325019227</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-9.626290031477165</v>
       </c>
       <c r="F60" t="n">
-        <v>9.662025267855759</v>
+        <v>7.269386802559395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.209354846377135</v>
+        <v>5.164321929536961</v>
       </c>
       <c r="H60" t="n">
-        <v>5.161235766003335</v>
+        <v>-24.50838200295205</v>
       </c>
       <c r="I60" t="n">
-        <v>3.641966304408245</v>
+        <v>22.0373973289976</v>
       </c>
       <c r="J60" t="n">
-        <v>5.482643734831568</v>
+        <v>-4.605859930188911</v>
       </c>
       <c r="K60" t="n">
-        <v>9.752432358082254</v>
+        <v>-4.80347294272176</v>
       </c>
     </row>
     <row r="61">
@@ -5911,28 +7126,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.978829017722484</v>
+        <v>3.695516207822149</v>
       </c>
       <c r="C61" t="n">
-        <v>-6.690870626357613</v>
+        <v>26.9443906811703</v>
+      </c>
+      <c r="D61" t="n">
+        <v>21.67237654654147</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10.30324158446168</v>
       </c>
       <c r="F61" t="n">
-        <v>9.815635614195573</v>
+        <v>7.57937968024346</v>
       </c>
       <c r="G61" t="n">
-        <v>3.319316514629362</v>
+        <v>5.556676280575195</v>
       </c>
       <c r="H61" t="n">
-        <v>5.438821772665267</v>
+        <v>-24.88746988169531</v>
       </c>
       <c r="I61" t="n">
-        <v>3.68172831652282</v>
+        <v>22.4238031898911</v>
       </c>
       <c r="J61" t="n">
-        <v>5.551949142961021</v>
+        <v>-4.660761660544321</v>
       </c>
       <c r="K61" t="n">
-        <v>10.14859149154484</v>
+        <v>-4.985644745974785</v>
       </c>
     </row>
     <row r="62">
@@ -5942,28 +7163,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4.058735065840393</v>
+        <v>3.827175591866572</v>
       </c>
       <c r="C62" t="n">
-        <v>-6.756237498541546</v>
+        <v>27.58989253581823</v>
+      </c>
+      <c r="D62" t="n">
+        <v>22.23796109919162</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-10.64005479216295</v>
       </c>
       <c r="F62" t="n">
-        <v>9.921880680741271</v>
+        <v>7.929307192400489</v>
       </c>
       <c r="G62" t="n">
-        <v>3.650032189696583</v>
+        <v>5.863356803546194</v>
       </c>
       <c r="H62" t="n">
-        <v>5.681394837434232</v>
+        <v>-25.32811363443056</v>
       </c>
       <c r="I62" t="n">
-        <v>3.657265745309827</v>
+        <v>23.1478031399945</v>
       </c>
       <c r="J62" t="n">
-        <v>5.529860672127827</v>
+        <v>-4.825879912580764</v>
       </c>
       <c r="K62" t="n">
-        <v>10.62270640984855</v>
+        <v>-5.192935527789068</v>
       </c>
     </row>
     <row r="63">
@@ -5973,34 +7200,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4.057902190462614</v>
+        <v>4.087948444228547</v>
       </c>
       <c r="C63" t="n">
-        <v>-6.720594001988809</v>
+        <v>28.11899195844323</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5486049313370529</v>
+        <v>22.41970200841348</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8484608480309851</v>
+        <v>-10.74324580045463</v>
       </c>
       <c r="F63" t="n">
-        <v>10.13566323288171</v>
+        <v>8.268652720729353</v>
       </c>
       <c r="G63" t="n">
-        <v>4.021829991601075</v>
+        <v>6.013886567598941</v>
       </c>
       <c r="H63" t="n">
-        <v>5.810704163581367</v>
+        <v>-25.78585022596313</v>
       </c>
       <c r="I63" t="n">
-        <v>3.814366493859801</v>
+        <v>23.43263804563271</v>
       </c>
       <c r="J63" t="n">
-        <v>5.576729206559895</v>
+        <v>-4.953992974646705</v>
       </c>
       <c r="K63" t="n">
-        <v>11.04959534526525</v>
+        <v>-5.400804960364608</v>
       </c>
     </row>
     <row r="64">
@@ -6010,34 +7237,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4.06709082123628</v>
+        <v>4.464573608260604</v>
       </c>
       <c r="C64" t="n">
-        <v>-6.823315994014548</v>
+        <v>28.65213435002228</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6211667672231235</v>
+        <v>22.88215084240023</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9319796730538882</v>
+        <v>-10.99552920448244</v>
       </c>
       <c r="F64" t="n">
-        <v>10.21638770898797</v>
+        <v>8.613299709617246</v>
       </c>
       <c r="G64" t="n">
-        <v>4.20123679648947</v>
+        <v>6.161068562277933</v>
       </c>
       <c r="H64" t="n">
-        <v>5.700566973508991</v>
+        <v>-26.19668677730339</v>
       </c>
       <c r="I64" t="n">
-        <v>3.808246537946732</v>
+        <v>24.02533240676275</v>
       </c>
       <c r="J64" t="n">
-        <v>5.666709031371783</v>
+        <v>-4.929401921708022</v>
       </c>
       <c r="K64" t="n">
-        <v>11.23886186799179</v>
+        <v>-5.330830475849005</v>
       </c>
     </row>
     <row r="65">
@@ -6047,28 +7274,34 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4.146996869354189</v>
+        <v>4.693175819383081</v>
       </c>
       <c r="C65" t="n">
-        <v>-6.893646248777894</v>
+        <v>29.15811950087048</v>
+      </c>
+      <c r="D65" t="n">
+        <v>23.35507224071502</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-11.34305837047473</v>
       </c>
       <c r="F65" t="n">
-        <v>10.33175355537963</v>
+        <v>9.001689103577689</v>
       </c>
       <c r="G65" t="n">
-        <v>4.368118319439296</v>
+        <v>6.501933162306916</v>
       </c>
       <c r="H65" t="n">
-        <v>5.745858685438296</v>
+        <v>-26.7454866160085</v>
       </c>
       <c r="I65" t="n">
-        <v>3.934232297205972</v>
+        <v>24.61541464083746</v>
       </c>
       <c r="J65" t="n">
-        <v>5.855817164547589</v>
+        <v>-5.260976075854011</v>
       </c>
       <c r="K65" t="n">
-        <v>11.71225648987244</v>
+        <v>-5.573737783563314</v>
       </c>
     </row>
     <row r="66">
@@ -6078,34 +7311,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4.268620468621284</v>
+        <v>4.992935403777582</v>
       </c>
       <c r="C66" t="n">
-        <v>-6.986416197830842</v>
+        <v>29.58074025706815</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6941662517241116</v>
+        <v>23.81302325954098</v>
       </c>
       <c r="E66" t="n">
-        <v>1.008897409050833</v>
+        <v>-11.66396797937959</v>
       </c>
       <c r="F66" t="n">
-        <v>10.52123350429352</v>
+        <v>9.352995426719959</v>
       </c>
       <c r="G66" t="n">
-        <v>4.646574193629572</v>
+        <v>6.749639029956718</v>
       </c>
       <c r="H66" t="n">
-        <v>5.942531014297943</v>
+        <v>-27.09774069507699</v>
       </c>
       <c r="I66" t="n">
-        <v>4.030998984790421</v>
+        <v>25.06302107335456</v>
       </c>
       <c r="J66" t="n">
-        <v>6.081193564371517</v>
+        <v>-5.330048492018384</v>
       </c>
       <c r="K66" t="n">
-        <v>12.03525551601491</v>
+        <v>-5.472572611850676</v>
       </c>
     </row>
     <row r="67">
@@ -6115,28 +7348,34 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.353127510874805</v>
+        <v>4.965504314378537</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.057765939791993</v>
+        <v>30.06158669399388</v>
+      </c>
+      <c r="D67" t="n">
+        <v>24.29170252801382</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-12.00294079791947</v>
       </c>
       <c r="F67" t="n">
-        <v>10.81059634669152</v>
+        <v>9.559342820733724</v>
       </c>
       <c r="G67" t="n">
-        <v>4.865339720756644</v>
+        <v>6.935398653289345</v>
       </c>
       <c r="H67" t="n">
-        <v>6.06040985090845</v>
+        <v>-27.62677350951682</v>
       </c>
       <c r="I67" t="n">
-        <v>4.271916721855631</v>
+        <v>25.61416861072144</v>
       </c>
       <c r="J67" t="n">
-        <v>6.194633257745689</v>
+        <v>-5.43101328664955</v>
       </c>
       <c r="K67" t="n">
-        <v>12.47793668605843</v>
+        <v>-5.64569631417827</v>
       </c>
     </row>
     <row r="68">
@@ -6146,28 +7385,34 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.435303211919435</v>
+        <v>5.146400480096043</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.126085337655761</v>
+        <v>30.5597969424544</v>
+      </c>
+      <c r="D68" t="n">
+        <v>24.85115776943782</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-12.30464715042691</v>
       </c>
       <c r="F68" t="n">
-        <v>11.03637420025918</v>
+        <v>9.882465595698578</v>
       </c>
       <c r="G68" t="n">
-        <v>4.864799526711744</v>
+        <v>7.004387258533354</v>
       </c>
       <c r="H68" t="n">
-        <v>6.045008930954603</v>
+        <v>-28.1159703178254</v>
       </c>
       <c r="I68" t="n">
-        <v>4.327496924091327</v>
+        <v>26.08866872325016</v>
       </c>
       <c r="J68" t="n">
-        <v>6.323150714074951</v>
+        <v>-5.630548668085515</v>
       </c>
       <c r="K68" t="n">
-        <v>12.85025050888558</v>
+        <v>-5.689498165313888</v>
       </c>
     </row>
     <row r="69">
@@ -6177,34 +7422,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.434470336541656</v>
+        <v>4.934892737774218</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.106676987877147</v>
+        <v>30.9002474991759</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7696083983558598</v>
+        <v>25.40844712527804</v>
       </c>
       <c r="E69" t="n">
-        <v>1.129330638709513</v>
+        <v>-12.36463784821207</v>
       </c>
       <c r="F69" t="n">
-        <v>11.25716201288341</v>
+        <v>10.0258001858763</v>
       </c>
       <c r="G69" t="n">
-        <v>5.171679367733256</v>
+        <v>6.777884820777403</v>
       </c>
       <c r="H69" t="n">
-        <v>6.361681889492019</v>
+        <v>-28.53591801530305</v>
       </c>
       <c r="I69" t="n">
-        <v>4.424206843125405</v>
+        <v>26.45368890467097</v>
       </c>
       <c r="J69" t="n">
-        <v>6.571410231116388</v>
+        <v>-5.597607573222244</v>
       </c>
       <c r="K69" t="n">
-        <v>13.33902696012297</v>
+        <v>-5.685552896152596</v>
       </c>
     </row>
     <row r="70">
@@ -6213,23 +7458,35 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>5.109337236190519</v>
+      </c>
+      <c r="C70" t="n">
+        <v>31.41202647330337</v>
+      </c>
+      <c r="D70" t="n">
+        <v>25.72422766341193</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-12.58582566605887</v>
+      </c>
       <c r="F70" t="n">
-        <v>11.37838729632955</v>
+        <v>10.47867943654117</v>
       </c>
       <c r="G70" t="n">
-        <v>5.407995338079827</v>
+        <v>7.024073815602195</v>
       </c>
       <c r="H70" t="n">
-        <v>6.43362366922026</v>
+        <v>-28.96698949969702</v>
       </c>
       <c r="I70" t="n">
-        <v>4.76000749866506</v>
+        <v>26.8504552534245</v>
       </c>
       <c r="J70" t="n">
-        <v>6.733575366827476</v>
+        <v>-5.752474996149326</v>
       </c>
       <c r="K70" t="n">
-        <v>13.63226138189162</v>
+        <v>-5.767881719980132</v>
       </c>
     </row>
     <row r="71">
@@ -6239,34 +7496,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4.521375812475543</v>
+        <v>5.504194037247603</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.177007242640492</v>
+        <v>31.88588382436196</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8245334240498935</v>
+        <v>26.2258080142294</v>
       </c>
       <c r="E71" t="n">
-        <v>1.210075301736082</v>
+        <v>-12.8339071402745</v>
       </c>
       <c r="F71" t="n">
-        <v>11.59248383655881</v>
+        <v>10.97300446518897</v>
       </c>
       <c r="G71" t="n">
-        <v>5.763692327828713</v>
+        <v>7.322277429557149</v>
       </c>
       <c r="H71" t="n">
-        <v>6.572216912422036</v>
+        <v>-29.40473854132223</v>
       </c>
       <c r="I71" t="n">
-        <v>4.907576037145295</v>
+        <v>27.31574139334281</v>
       </c>
       <c r="J71" t="n">
-        <v>6.875412618673957</v>
+        <v>-5.986995042586771</v>
       </c>
       <c r="K71" t="n">
-        <v>13.84795259508148</v>
+        <v>-5.981241732723576</v>
       </c>
     </row>
     <row r="72">
@@ -6275,23 +7532,35 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="B72" t="n">
+        <v>5.715490238195499</v>
+      </c>
+      <c r="C72" t="n">
+        <v>32.25981832651897</v>
+      </c>
+      <c r="D72" t="n">
+        <v>26.60795694268195</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-13.02245557944896</v>
+      </c>
       <c r="F72" t="n">
-        <v>11.92898830144781</v>
+        <v>11.36995397576043</v>
       </c>
       <c r="G72" t="n">
-        <v>5.910779581254142</v>
+        <v>7.660321059411897</v>
       </c>
       <c r="H72" t="n">
-        <v>6.676879851324228</v>
+        <v>-29.8733121766475</v>
       </c>
       <c r="I72" t="n">
-        <v>5.094737197092554</v>
+        <v>27.70090079881202</v>
       </c>
       <c r="J72" t="n">
-        <v>6.896772423678813</v>
+        <v>-6.033267688867506</v>
       </c>
       <c r="K72" t="n">
-        <v>14.06633569334591</v>
+        <v>-6.04783691070149</v>
       </c>
     </row>
     <row r="73">
@@ -6300,23 +7569,35 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>5.807371066033952</v>
+      </c>
+      <c r="C73" t="n">
+        <v>32.64139430644239</v>
+      </c>
+      <c r="D73" t="n">
+        <v>27.17965885176044</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-13.40028267574269</v>
+      </c>
       <c r="F73" t="n">
-        <v>12.05877352777637</v>
+        <v>11.3172611431358</v>
       </c>
       <c r="G73" t="n">
-        <v>6.020936645627851</v>
+        <v>7.598430934937185</v>
       </c>
       <c r="H73" t="n">
-        <v>6.941934102508231</v>
+        <v>-30.3553144540679</v>
       </c>
       <c r="I73" t="n">
-        <v>5.242003908805852</v>
+        <v>28.20096953753756</v>
       </c>
       <c r="J73" t="n">
-        <v>7.003479407261994</v>
+        <v>-6.044268671047021</v>
       </c>
       <c r="K73" t="n">
-        <v>14.37004100555878</v>
+        <v>-6.041710145891761</v>
       </c>
     </row>
     <row r="74">
@@ -6325,23 +7606,35 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>6.027790133026854</v>
+      </c>
+      <c r="C74" t="n">
+        <v>33.20163854384803</v>
+      </c>
+      <c r="D74" t="n">
+        <v>27.59094225710434</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-13.6663718259997</v>
+      </c>
       <c r="F74" t="n">
-        <v>12.2870594206236</v>
+        <v>11.78509805580451</v>
       </c>
       <c r="G74" t="n">
-        <v>6.294922086681675</v>
+        <v>7.892155021390887</v>
       </c>
       <c r="H74" t="n">
-        <v>7.084269239513586</v>
+        <v>-30.81154780432722</v>
       </c>
       <c r="I74" t="n">
-        <v>5.525472572637502</v>
+        <v>28.70498746124982</v>
       </c>
       <c r="J74" t="n">
-        <v>7.063097830633896</v>
+        <v>-6.269318528377901</v>
       </c>
       <c r="K74" t="n">
-        <v>14.73381194983391</v>
+        <v>-6.154109282884344</v>
       </c>
     </row>
     <row r="75">
@@ -6350,23 +7643,35 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>6.019361068236742</v>
+      </c>
+      <c r="C75" t="n">
+        <v>33.72562615804168</v>
+      </c>
+      <c r="D75" t="n">
+        <v>28.04275661902517</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-13.80704062418472</v>
+      </c>
       <c r="F75" t="n">
-        <v>12.37612557815891</v>
+        <v>11.86590573459315</v>
       </c>
       <c r="G75" t="n">
-        <v>6.535075185265566</v>
+        <v>7.578290751476467</v>
       </c>
       <c r="H75" t="n">
-        <v>7.242254893340676</v>
+        <v>-31.28510835169018</v>
       </c>
       <c r="I75" t="n">
-        <v>5.61269133281695</v>
+        <v>29.06795426280579</v>
       </c>
       <c r="J75" t="n">
-        <v>7.155635347463344</v>
+        <v>-6.433346911957135</v>
       </c>
       <c r="K75" t="n">
-        <v>15.20947191118817</v>
+        <v>-5.983185998877065</v>
       </c>
     </row>
     <row r="76">
@@ -6376,34 +7681,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4.605882854729064</v>
+        <v>6.558566587011712</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.081088717468607</v>
+        <v>34.0305511036209</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9111542632980237</v>
+        <v>28.27082781018172</v>
       </c>
       <c r="E76" t="n">
-        <v>1.280824689132561</v>
+        <v>-14.39599310318297</v>
       </c>
       <c r="F76" t="n">
-        <v>12.41046677852909</v>
+        <v>12.3008635381948</v>
       </c>
       <c r="G76" t="n">
-        <v>6.510032387586433</v>
+        <v>7.897615936278239</v>
       </c>
       <c r="H76" t="n">
-        <v>7.347893161534845</v>
+        <v>-31.74243415304034</v>
       </c>
       <c r="I76" t="n">
-        <v>5.79853458317077</v>
+        <v>29.62675368998264</v>
       </c>
       <c r="J76" t="n">
-        <v>7.187508254484488</v>
+        <v>-6.577947913345497</v>
       </c>
       <c r="K76" t="n">
-        <v>15.5259936930299</v>
+        <v>-6.013470158013845</v>
       </c>
     </row>
     <row r="77">
@@ -6412,23 +7717,35 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>6.701954046181286</v>
+      </c>
+      <c r="C77" t="n">
+        <v>34.6143957032772</v>
+      </c>
+      <c r="D77" t="n">
+        <v>28.81528977536868</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-14.56552239284525</v>
+      </c>
       <c r="F77" t="n">
-        <v>12.62354479243463</v>
+        <v>12.6294515671602</v>
       </c>
       <c r="G77" t="n">
-        <v>6.752091251772218</v>
+        <v>8.092335510339629</v>
       </c>
       <c r="H77" t="n">
-        <v>7.509489055532474</v>
+        <v>-32.30331882843648</v>
       </c>
       <c r="I77" t="n">
-        <v>5.740801413471389</v>
+        <v>30.22103532373757</v>
       </c>
       <c r="J77" t="n">
-        <v>7.188036437788309</v>
+        <v>-6.786742285608113</v>
       </c>
       <c r="K77" t="n">
-        <v>15.87688443288286</v>
+        <v>-6.150909994207236</v>
       </c>
     </row>
     <row r="78">
@@ -6437,23 +7754,35 @@
           <t>2025-12-30</t>
         </is>
       </c>
+      <c r="B78" t="n">
+        <v>6.700044953553652</v>
+      </c>
+      <c r="C78" t="n">
+        <v>35.16260706277995</v>
+      </c>
+      <c r="D78" t="n">
+        <v>29.27004516244656</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-14.66588140116761</v>
+      </c>
       <c r="F78" t="n">
-        <v>12.69133448423083</v>
+        <v>12.76248094184808</v>
       </c>
       <c r="G78" t="n">
-        <v>6.637346775527959</v>
+        <v>8.137282527539947</v>
       </c>
       <c r="H78" t="n">
-        <v>7.529423029923327</v>
+        <v>-32.84349018084688</v>
       </c>
       <c r="I78" t="n">
-        <v>5.854172244233401</v>
+        <v>30.67096455932553</v>
       </c>
       <c r="J78" t="n">
-        <v>7.257180487005012</v>
+        <v>-6.713856684973317</v>
       </c>
       <c r="K78" t="n">
-        <v>16.09859143895914</v>
+        <v>-6.108943366902627</v>
       </c>
     </row>
     <row r="79">
@@ -6462,23 +7791,35 @@
           <t>2026-01-14</t>
         </is>
       </c>
+      <c r="B79" t="n">
+        <v>6.882807249611983</v>
+      </c>
+      <c r="C79" t="n">
+        <v>35.68829599748576</v>
+      </c>
+      <c r="D79" t="n">
+        <v>29.88199912399786</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-14.92940183639036</v>
+      </c>
       <c r="F79" t="n">
-        <v>12.92490991515819</v>
+        <v>13.18832290679524</v>
       </c>
       <c r="G79" t="n">
-        <v>6.889679305524393</v>
+        <v>8.406308101839866</v>
       </c>
       <c r="H79" t="n">
-        <v>7.750910791328245</v>
+        <v>-33.19950934715526</v>
       </c>
       <c r="I79" t="n">
-        <v>6.081633041753977</v>
+        <v>31.27855238302168</v>
       </c>
       <c r="J79" t="n">
-        <v>7.382304504737396</v>
+        <v>-6.656545005660043</v>
       </c>
       <c r="K79" t="n">
-        <v>16.51160002796551</v>
+        <v>-6.163836202076638</v>
       </c>
     </row>
     <row r="80">
@@ -6487,23 +7828,35 @@
           <t>2026-01-29</t>
         </is>
       </c>
+      <c r="B80" t="n">
+        <v>6.96294116171489</v>
+      </c>
+      <c r="C80" t="n">
+        <v>36.34050567451484</v>
+      </c>
+      <c r="D80" t="n">
+        <v>30.4004655035465</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-15.16054851640148</v>
+      </c>
       <c r="F80" t="n">
-        <v>13.17653962435113</v>
+        <v>13.56817516016292</v>
       </c>
       <c r="G80" t="n">
-        <v>7.210513700529605</v>
+        <v>8.67719325727305</v>
       </c>
       <c r="H80" t="n">
-        <v>7.869956635577206</v>
+        <v>-33.61148106515609</v>
       </c>
       <c r="I80" t="n">
-        <v>6.292756604298047</v>
+        <v>31.92904212313577</v>
       </c>
       <c r="J80" t="n">
-        <v>7.531330931465108</v>
+        <v>-6.816484010944673</v>
       </c>
       <c r="K80" t="n">
-        <v>17.13054208972724</v>
+        <v>-6.253584395972571</v>
       </c>
     </row>
     <row r="81">
@@ -6513,34 +7866,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4.685788902846973</v>
+        <v>7.344117622857717</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.158781814355158</v>
+        <v>36.89587710526273</v>
       </c>
       <c r="D81" t="n">
-        <v>1.009110475360192</v>
+        <v>31.07232438735059</v>
       </c>
       <c r="E81" t="n">
-        <v>1.362562865269334</v>
+        <v>-15.55151453631406</v>
       </c>
       <c r="F81" t="n">
-        <v>13.41205364390842</v>
+        <v>14.18134139436831</v>
       </c>
       <c r="G81" t="n">
-        <v>7.137090013122871</v>
+        <v>8.822181392228806</v>
       </c>
       <c r="H81" t="n">
-        <v>7.872243143348505</v>
+        <v>-34.16796793600246</v>
       </c>
       <c r="I81" t="n">
-        <v>6.460705093687737</v>
+        <v>32.35773592644463</v>
       </c>
       <c r="J81" t="n">
-        <v>7.697737204155997</v>
+        <v>-7.102892926051092</v>
       </c>
       <c r="K81" t="n">
-        <v>17.54858118393304</v>
+        <v>-6.329313143127416</v>
       </c>
     </row>
     <row r="82">
@@ -6549,23 +7902,35 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="B82" t="n">
+        <v>7.389741407327376</v>
+      </c>
+      <c r="C82" t="n">
+        <v>37.39383754818266</v>
+      </c>
+      <c r="D82" t="n">
+        <v>31.50089956991932</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-15.60610528335758</v>
+      </c>
       <c r="F82" t="n">
-        <v>13.56795631676657</v>
+        <v>14.57163003090494</v>
       </c>
       <c r="G82" t="n">
-        <v>7.302353422339711</v>
+        <v>9.022736788747563</v>
       </c>
       <c r="H82" t="n">
-        <v>8.041269149587526</v>
+        <v>-34.64436930144657</v>
       </c>
       <c r="I82" t="n">
-        <v>6.6729830767648</v>
+        <v>32.86520153839177</v>
       </c>
       <c r="J82" t="n">
-        <v>7.758559763357158</v>
+        <v>-7.285388319745086</v>
       </c>
       <c r="K82" t="n">
-        <v>17.66852330976678</v>
+        <v>-6.417264285072664</v>
       </c>
     </row>
     <row r="83">
@@ -6574,23 +7939,35 @@
           <t>2026-03-13</t>
         </is>
       </c>
+      <c r="B83" t="n">
+        <v>7.471779980838161</v>
+      </c>
+      <c r="C83" t="n">
+        <v>37.81238506650733</v>
+      </c>
+      <c r="D83" t="n">
+        <v>31.86675281660009</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-15.81084986898661</v>
+      </c>
       <c r="F83" t="n">
-        <v>13.72745700322744</v>
+        <v>14.90300324679581</v>
       </c>
       <c r="G83" t="n">
-        <v>7.320739179956524</v>
+        <v>9.215202782534949</v>
       </c>
       <c r="H83" t="n">
-        <v>8.106986201028048</v>
+        <v>-35.20974687624404</v>
       </c>
       <c r="I83" t="n">
-        <v>6.852382628350147</v>
+        <v>33.28573581458064</v>
       </c>
       <c r="J83" t="n">
-        <v>7.968937163294984</v>
+        <v>-7.359654047598077</v>
       </c>
       <c r="K83" t="n">
-        <v>18.08874734440142</v>
+        <v>-6.47311146056913</v>
       </c>
     </row>
     <row r="84">
@@ -6599,23 +7976,35 @@
           <t>2026-03-27</t>
         </is>
       </c>
+      <c r="B84" t="n">
+        <v>7.787462354735013</v>
+      </c>
+      <c r="C84" t="n">
+        <v>38.38682635967436</v>
+      </c>
+      <c r="D84" t="n">
+        <v>32.3818137274848</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-16.09441309869589</v>
+      </c>
       <c r="F84" t="n">
-        <v>13.7095716711787</v>
+        <v>15.23706018909854</v>
       </c>
       <c r="G84" t="n">
-        <v>7.110135601393591</v>
+        <v>9.39407021089761</v>
       </c>
       <c r="H84" t="n">
-        <v>8.076501677005027</v>
+        <v>-35.73305890248145</v>
       </c>
       <c r="I84" t="n">
-        <v>6.957891323324007</v>
+        <v>33.75488162869953</v>
       </c>
       <c r="J84" t="n">
-        <v>8.030473996672589</v>
+        <v>-7.505517621724259</v>
       </c>
       <c r="K84" t="n">
-        <v>18.269929964764</v>
+        <v>-6.482860551523982</v>
       </c>
     </row>
     <row r="85">
@@ -6624,23 +8013,35 @@
           <t>2026-04-13</t>
         </is>
       </c>
+      <c r="B85" t="n">
+        <v>8.161570654197099</v>
+      </c>
+      <c r="C85" t="n">
+        <v>38.69556315633502</v>
+      </c>
+      <c r="D85" t="n">
+        <v>32.88250999811412</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-16.65104148107739</v>
+      </c>
       <c r="F85" t="n">
-        <v>13.93943592108616</v>
+        <v>15.7716578467662</v>
       </c>
       <c r="G85" t="n">
-        <v>7.455143425513561</v>
+        <v>9.751090004075699</v>
       </c>
       <c r="H85" t="n">
-        <v>8.314811483994189</v>
+        <v>-36.06641406818756</v>
       </c>
       <c r="I85" t="n">
-        <v>7.149302344233706</v>
+        <v>34.0036113555941</v>
       </c>
       <c r="J85" t="n">
-        <v>8.17992373544825</v>
+        <v>-7.78458357461386</v>
       </c>
       <c r="K85" t="n">
-        <v>18.62476109379206</v>
+        <v>-6.619800840151268</v>
       </c>
     </row>
     <row r="86">
@@ -6649,23 +8050,35 @@
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="B86" t="n">
+        <v>8.122986162136444</v>
+      </c>
+      <c r="C86" t="n">
+        <v>39.0803771401827</v>
+      </c>
+      <c r="D86" t="n">
+        <v>33.2773759605979</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-16.86366160379852</v>
+      </c>
       <c r="F86" t="n">
-        <v>14.29880407788459</v>
+        <v>16.26838085186762</v>
       </c>
       <c r="G86" t="n">
-        <v>7.760608595167916</v>
+        <v>9.800801331390865</v>
       </c>
       <c r="H86" t="n">
-        <v>8.393878489774933</v>
+        <v>-36.48995243386452</v>
       </c>
       <c r="I86" t="n">
-        <v>7.260044097427393</v>
+        <v>34.21267504978751</v>
       </c>
       <c r="J86" t="n">
-        <v>8.251156674793823</v>
+        <v>-8.075022919435691</v>
       </c>
       <c r="K86" t="n">
-        <v>18.76864663927526</v>
+        <v>-6.717835918268565</v>
       </c>
     </row>
     <row r="87">
@@ -6674,23 +8087,35 @@
           <t>2026-05-11</t>
         </is>
       </c>
+      <c r="B87" t="n">
+        <v>8.671811129844405</v>
+      </c>
+      <c r="C87" t="n">
+        <v>39.76171111865128</v>
+      </c>
+      <c r="D87" t="n">
+        <v>33.70888181714716</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-17.3360127108167</v>
+      </c>
       <c r="F87" t="n">
-        <v>14.48659913507655</v>
+        <v>17.01821112787975</v>
       </c>
       <c r="G87" t="n">
-        <v>8.093297023866191</v>
+        <v>10.16835039818913</v>
       </c>
       <c r="H87" t="n">
-        <v>8.458029436771891</v>
+        <v>-36.9907678654776</v>
       </c>
       <c r="I87" t="n">
-        <v>7.331780393293664</v>
+        <v>34.67172148116115</v>
       </c>
       <c r="J87" t="n">
-        <v>8.336650628420097</v>
+        <v>-8.494177429611337</v>
       </c>
       <c r="K87" t="n">
-        <v>19.07792972186829</v>
+        <v>-6.877972391338128</v>
       </c>
     </row>
     <row r="88">
@@ -6699,23 +8124,146 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="B88" t="n">
+        <v>8.875035545656331</v>
+      </c>
+      <c r="C88" t="n">
+        <v>40.24870443192936</v>
+      </c>
+      <c r="D88" t="n">
+        <v>34.22815065843336</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-17.78953917680132</v>
+      </c>
       <c r="F88" t="n">
-        <v>14.59744774790497</v>
+        <v>17.60106664377507</v>
       </c>
       <c r="G88" t="n">
-        <v>8.268811296974595</v>
+        <v>10.6299159218895</v>
       </c>
       <c r="H88" t="n">
-        <v>8.439828731338094</v>
+        <v>-37.29993110586729</v>
       </c>
       <c r="I88" t="n">
-        <v>7.412191597809185</v>
+        <v>35.32277435028696</v>
       </c>
       <c r="J88" t="n">
-        <v>8.382987018031312</v>
+        <v>-8.730565555258686</v>
       </c>
       <c r="K88" t="n">
-        <v>19.45749470970719</v>
+        <v>-7.085638017160129</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>9.395430968409689</v>
+      </c>
+      <c r="C89" t="n">
+        <v>40.93442899184813</v>
+      </c>
+      <c r="D89" t="n">
+        <v>34.7425176662865</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-17.95597631897704</v>
+      </c>
+      <c r="F89" t="n">
+        <v>18.16074998234197</v>
+      </c>
+      <c r="G89" t="n">
+        <v>11.15899419515758</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-37.60959271372579</v>
+      </c>
+      <c r="I89" t="n">
+        <v>35.82079389394494</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-8.980974419110385</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-7.086214315459737</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9.746820774621296</v>
+      </c>
+      <c r="C90" t="n">
+        <v>41.3743174725521</v>
+      </c>
+      <c r="D90" t="n">
+        <v>35.17305306042459</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-18.25164813209909</v>
+      </c>
+      <c r="F90" t="n">
+        <v>18.70635635395124</v>
+      </c>
+      <c r="G90" t="n">
+        <v>11.60909655919578</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-37.92818797088562</v>
+      </c>
+      <c r="I90" t="n">
+        <v>36.34244158658502</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-9.174230471299463</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-7.264542571829453</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10.05416148788821</v>
+      </c>
+      <c r="C91" t="n">
+        <v>41.66466759428189</v>
+      </c>
+      <c r="D91" t="n">
+        <v>35.5206811288614</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-18.45966870408864</v>
+      </c>
+      <c r="F91" t="n">
+        <v>19.12233264397757</v>
+      </c>
+      <c r="G91" t="n">
+        <v>11.71430339051245</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-38.18406428561499</v>
+      </c>
+      <c r="I91" t="n">
+        <v>36.63458015026888</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-9.392007723098203</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-7.399013339732602</v>
       </c>
     </row>
   </sheetData>
